--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\小红叔\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D124A5-D760-4075-AA1A-810BD89D5409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D64385-D922-4353-9D51-BC362B2F7ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
   <sheets>
-    <sheet name="template" sheetId="1" r:id="rId1"/>
+    <sheet name="template" sheetId="3" r:id="rId1"/>
     <sheet name="readme" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="124">
   <si>
     <t>请 假 单</t>
   </si>
@@ -96,7 +96,7 @@
       </rPr>
       <t>包住）</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>行级（逐条记录，会被每条记录替换一次）</t>
@@ -142,7 +142,7 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>J2609001 / G2609001</t>
@@ -173,7 +173,7 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>人员</t>
@@ -224,7 +224,7 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>业务日期</t>
@@ -270,7 +270,7 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>起-止整段</t>
@@ -298,7 +298,7 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>工时</t>
@@ -329,7 +329,7 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>事由/备注</t>
@@ -390,7 +390,7 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -415,7 +415,7 @@
       </rPr>
       <t>}}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>当前时间</t>
@@ -452,7 +452,7 @@
       </rPr>
       <t>}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>本次导出记录数</t>
@@ -489,7 +489,7 @@
       </rPr>
       <t>}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>工时合计</t>
@@ -517,7 +517,7 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>当前筛选的考勤组</t>
@@ -545,7 +545,7 @@
       </rPr>
       <t>}}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>当前类别</t>
@@ -573,7 +573,7 @@
       </rPr>
       <t>}}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>当前状态筛选</t>
@@ -631,7 +631,7 @@
   </si>
   <si>
     <t>注意：</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>多人记录的取舍：{{姓名}} 会列出全部人员，但工号/性别/部门这类字段只取第一位人员（拼成一串没意义）。请假/加班申请单通常是一人一单，不受影响。</t>
@@ -662,7 +662,7 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -687,15 +687,15 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{{说明}}</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>起始时间</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -720,7 +720,7 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -745,35 +745,35 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>自{{起日期}} {{开始}}</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>至{{至日期}} {{结束}}</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">{{起日期}} </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">{{至日期}} </t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>多日请假的起日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>多日请假的至日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>MM-DD</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -795,7 +795,7 @@
       </rPr>
       <t xml:space="preserve"> 08:30~17:00</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -817,19 +817,19 @@
       </rPr>
       <t xml:space="preserve"> YYYY-MM-DD</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>人员/签名占位符（签名图片文件为.\names下对应姓名的jpg文件）</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>记录对应人员的签名，</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>签名占位符</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -844,11 +844,11 @@
       </rPr>
       <t>}}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>也可指定人员签名</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -873,11 +873,11 @@
       </rPr>
       <t>}}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>设置里面考勤组的相应绑定人员</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -902,7 +902,7 @@
       </rPr>
       <t>}}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -927,7 +927,7 @@
       </rPr>
       <t>}}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -952,11 +952,11 @@
       </rPr>
       <t>}}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>姓名文字</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -981,7 +981,7 @@
       </rPr>
       <t>}}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1006,11 +1006,11 @@
       </rPr>
       <t>}}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>记录存储里时间是以 {{时段}}（"08:30~17:00"）整体存的，{{开始}}/{{结束}} 自动解析；</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1035,11 +1035,11 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>请假类别</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1064,87 +1064,83 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>姓名：</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>部门：</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>职别：</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>代理人：</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>请假事由</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>如果“请假类别”为“其它”，请在“请假事由”中备注情况</t>
   </si>
   <si>
-    <t>{{类别}} □</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>{{{一级部门}}}</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{{姓名}}</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>共{{小时}}小时</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>请假人:</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{{签名}}</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>部门经理：</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">{{类别}} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☑</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
-      <name val="新宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="ˎ̥"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1212,12 +1208,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="14"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -1238,14 +1228,50 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="12"/>
       <name val="仿宋"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
+      <sz val="16"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <name val="仿宋"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="ˎ̥"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <name val="新宋体"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -1552,173 +1578,176 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1755,10 +1784,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1076" name="Line 1">
+        <xdr:cNvPr id="2" name="Line 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56C91A6A-810C-0D48-0B0D-62BFD22A2795}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18ED17A1-919D-4131-8AA9-5BA9E9E362B6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1768,8 +1797,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1438275" y="2657475"/>
-          <a:ext cx="0" cy="419100"/>
+          <a:off x="1819275" y="2800350"/>
+          <a:ext cx="0" cy="981075"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1809,10 +1838,10 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1078" name="Line 1">
+        <xdr:cNvPr id="3" name="Line 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55CA5816-CA60-56F6-B131-1272E5438A74}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5FB8E98-3F47-4A77-AEA7-8DB83B5C8ED7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1822,7 +1851,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3086100" y="2638425"/>
+          <a:off x="3638550" y="2781300"/>
           <a:ext cx="0" cy="419100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -2137,192 +2166,194 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71AD2D6B-727C-4D0A-B04A-D7477CEFC907}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD1811D-72BB-4F54-B90A-4D27DF8394AD}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="7.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="7.5" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7.5" customWidth="1"/>
+    <col min="4" max="4" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="7.5" customWidth="1"/>
+    <col min="7" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.5" customWidth="1"/>
+    <col min="10" max="10" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="7.5" customWidth="1"/>
+    <col min="13" max="13" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="50.25" customHeight="1" thickBot="1">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:13" ht="50.25" customHeight="1" thickBot="1">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-    </row>
-    <row r="2" spans="1:12" ht="42" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+    </row>
+    <row r="2" spans="1:13" ht="54" customHeight="1">
+      <c r="A2" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="34" t="s">
+      <c r="B2" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="F2" s="39"/>
-      <c r="G2" s="34" t="s">
+      <c r="E2" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="F2" s="25"/>
+      <c r="G2" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="H2" s="35"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="34" t="s">
+      <c r="H2" s="28"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="K2" s="35"/>
-      <c r="L2" s="36"/>
-    </row>
-    <row r="3" spans="1:12" ht="42" customHeight="1">
+      <c r="K2" s="28"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="54" customHeight="1">
       <c r="A3" s="31" t="s">
         <v>114</v>
       </c>
       <c r="B3" s="32"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="40" t="s">
+      <c r="C3" s="33"/>
+      <c r="D3" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="42"/>
-    </row>
-    <row r="4" spans="1:12" ht="42" customHeight="1">
-      <c r="A4" s="25" t="s">
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="36"/>
+    </row>
+    <row r="4" spans="1:13" ht="54" customHeight="1">
+      <c r="A4" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="45" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="35"/>
+      <c r="F4" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="46"/>
-    </row>
-    <row r="5" spans="1:12" ht="42" customHeight="1">
-      <c r="A5" s="22" t="s">
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="56"/>
+    </row>
+    <row r="5" spans="1:13" ht="54" customHeight="1">
+      <c r="A5" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="40" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="40" t="s">
+      <c r="E5" s="35"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="H5" s="41"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="48" t="s">
+      <c r="H5" s="35"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="K5" s="45"/>
+      <c r="L5" s="46"/>
+    </row>
+    <row r="6" spans="1:13" ht="66" customHeight="1" thickBot="1">
+      <c r="A6" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="48"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="48"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="52" t="s">
         <v>119</v>
       </c>
-      <c r="K5" s="43"/>
-      <c r="L5" s="44"/>
-    </row>
-    <row r="6" spans="1:12" ht="78.75" customHeight="1" thickBot="1">
-      <c r="A6" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="52"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="53" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="52"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="54" t="s">
+      <c r="K6" s="48" t="s">
         <v>120</v>
       </c>
-      <c r="K6" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="L6" s="55"/>
-    </row>
-    <row r="7" spans="1:12" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A7" s="24" t="s">
+      <c r="L6" s="53"/>
+    </row>
+    <row r="7" spans="1:13" ht="33.75" customHeight="1">
+      <c r="A7" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="K6:L6"/>
     <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:L4"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="A3:C3"/>
     <mergeCell ref="D3:L3"/>
-    <mergeCell ref="A6:B6"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" scale="83" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
+  <pageSetup paperSize="11" scale="82" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -2338,495 +2369,495 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="5"/>
+      <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="5"/>
+      <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="14" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="5"/>
+      <c r="C34" s="4"/>
     </row>
     <row r="35" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="5"/>
+      <c r="C35" s="4"/>
     </row>
     <row r="36" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="5"/>
+      <c r="C36" s="4"/>
     </row>
     <row r="37" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="5"/>
+      <c r="C37" s="4"/>
     </row>
     <row r="38" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C38" s="5"/>
+      <c r="C38" s="4"/>
     </row>
     <row r="39" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="5"/>
+      <c r="C39" s="4"/>
     </row>
     <row r="40" spans="1:3" ht="16.5">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="13" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="41.25" customHeight="1" thickBot="1">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="13" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="13" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="33.75" thickBot="1">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="13" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="33.75" thickBot="1">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="13" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="19" t="s">
+      <c r="C46" s="18" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="33.75" thickBot="1">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="18" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="33.75" thickBot="1">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" s="18" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="16.5">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
         <v>1</v>
       </c>
-      <c r="B50" s="21" t="s">
+      <c r="B50" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="20"/>
+      <c r="C50" s="19"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <v>2</v>
       </c>
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="C51" s="20"/>
+      <c r="C51" s="19"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
         <v>3</v>
       </c>
-      <c r="B52" s="20" t="s">
+      <c r="B52" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C52" s="20"/>
+      <c r="C52" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2839,7 +2870,7 @@
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A40:C40"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\小红叔\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D64385-D922-4353-9D51-BC362B2F7ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7618FB-DD0C-4629-9164-E7534F9FE47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="123">
   <si>
     <t>请 假 单</t>
   </si>
@@ -748,14 +748,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>自{{起日期}} {{开始}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>至{{至日期}} {{结束}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">{{起日期}} </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1098,10 +1090,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>共{{小时}}小时</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>请假人:</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1115,20 +1103,89 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">{{类别}} </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
+      <t>共</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{{小时}}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小时</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>至</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{{至日期}} {{结束}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>自</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{{起日期}} {{开始}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{{类别}}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
         <rFont val="Segoe UI Symbol"/>
         <family val="2"/>
       </rPr>
       <t>☑</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>X</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1229,41 +1286,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="仿宋"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <name val="仿宋"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <name val="ˎ̥"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1272,6 +1295,41 @@
       <b/>
       <sz val="26"/>
       <name val="新宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="仿宋"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="ˎ̥"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="仿宋"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -1296,7 +1354,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1563,22 +1621,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1603,6 +1652,33 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1615,139 +1691,118 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2173,169 +2228,173 @@
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="4" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="7.5" customWidth="1"/>
-    <col min="7" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="7.5" customWidth="1"/>
-    <col min="10" max="10" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.375" customWidth="1"/>
     <col min="11" max="12" width="7.5" customWidth="1"/>
     <col min="13" max="13" width="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="50.25" customHeight="1" thickBot="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
     </row>
     <row r="2" spans="1:13" ht="54" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2" s="58"/>
+      <c r="G2" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="H2" s="38"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="K2" s="38"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="22"/>
+    </row>
+    <row r="3" spans="1:13" ht="54" customHeight="1">
+      <c r="A3" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="23"/>
+    </row>
+    <row r="4" spans="1:13" ht="71.25" customHeight="1">
+      <c r="A4" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="28"/>
+      <c r="F4" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="23"/>
+    </row>
+    <row r="5" spans="1:13" ht="54" customHeight="1">
+      <c r="A5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="32"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="28"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="28"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="K5" s="54"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="23"/>
+    </row>
+    <row r="6" spans="1:13" ht="66" customHeight="1" thickBot="1">
+      <c r="A6" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="47"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="47"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="47"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="K6" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="F2" s="25"/>
-      <c r="G2" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="H2" s="28"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="K2" s="28"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="22" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="54" customHeight="1">
-      <c r="A3" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="36"/>
-    </row>
-    <row r="4" spans="1:13" ht="54" customHeight="1">
-      <c r="A4" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="E4" s="35"/>
-      <c r="F4" s="55" t="s">
-        <v>115</v>
-      </c>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="56"/>
-    </row>
-    <row r="5" spans="1:13" ht="54" customHeight="1">
-      <c r="A5" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" s="35"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="H5" s="35"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="K5" s="45"/>
-      <c r="L5" s="46"/>
-    </row>
-    <row r="6" spans="1:13" ht="66" customHeight="1" thickBot="1">
-      <c r="A6" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="50" t="s">
-        <v>121</v>
-      </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="50" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="48"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="K6" s="48" t="s">
-        <v>120</v>
-      </c>
-      <c r="L6" s="53"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="23"/>
     </row>
     <row r="7" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:L4"/>
@@ -2343,17 +2402,15 @@
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:L5"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="A7:L7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" scale="82" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="11" scale="77" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -2369,18 +2426,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2434,29 +2491,29 @@
         <v>20</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.25" thickBot="1">
       <c r="A9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="C9" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.25" thickBot="1">
       <c r="A10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>89</v>
-      </c>
       <c r="C10" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17.25" thickBot="1">
@@ -2474,7 +2531,7 @@
       <c r="A12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="8" t="s">
         <v>81</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -2499,8 +2556,8 @@
       <c r="B14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>91</v>
+      <c r="C14" s="10" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17.25" thickBot="1">
@@ -2534,7 +2591,7 @@
     </row>
     <row r="18" spans="1:3" ht="17.25" thickBot="1">
       <c r="A18" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>36</v>
@@ -2566,11 +2623,11 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
       <c r="A22" s="1" t="s">
@@ -2584,8 +2641,8 @@
       <c r="A23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>92</v>
+      <c r="B23" s="10" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="17.25" thickBot="1">
@@ -2637,11 +2694,11 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
       <c r="A31" s="1" t="s">
@@ -2731,98 +2788,98 @@
       <c r="C39" s="4"/>
     </row>
     <row r="40" spans="1:3" ht="16.5">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+    </row>
+    <row r="41" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A41" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-    </row>
-    <row r="41" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A41" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B41" s="17" t="s">
+    </row>
+    <row r="42" spans="1:3" ht="41.25" customHeight="1" thickBot="1">
+      <c r="A42" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="B42" s="12" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="41.25" customHeight="1" thickBot="1">
-      <c r="A42" s="16" t="s">
+      <c r="C42" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A43" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B43" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A43" s="16" t="s">
+      <c r="C43" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="33.75" thickBot="1">
+      <c r="A44" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B44" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="33.75" thickBot="1">
+      <c r="A45" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="33.75" thickBot="1">
-      <c r="A44" s="16" t="s">
+      <c r="B45" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A46" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B44" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="33.75" thickBot="1">
-      <c r="A45" s="16" t="s">
+      <c r="B46" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="B45" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A46" s="16" t="s">
+    </row>
+    <row r="47" spans="1:3" ht="33.75" thickBot="1">
+      <c r="A47" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B46" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" s="18" t="s">
+      <c r="B47" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="33.75" thickBot="1">
+      <c r="A48" s="11" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" ht="33.75" thickBot="1">
-      <c r="A47" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="C47" s="18" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="33.75" thickBot="1">
-      <c r="A48" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" s="18" t="s">
-        <v>103</v>
+      <c r="B48" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="16.5">
@@ -2836,28 +2893,28 @@
       <c r="A50">
         <v>1</v>
       </c>
-      <c r="B50" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="C50" s="19"/>
+      <c r="B50" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="16"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <v>2</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C51" s="19"/>
+      <c r="C51" s="16"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
         <v>3</v>
       </c>
-      <c r="B52" s="19" t="s">
+      <c r="B52" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="C52" s="19"/>
+      <c r="C52" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\小红叔\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7618FB-DD0C-4629-9164-E7534F9FE47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB419F9-DA41-431B-BEFD-36CAE1C1687F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="3" r:id="rId1"/>
@@ -690,10 +690,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{{说明}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>起始时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1102,9 +1098,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>共</t>
-    </r>
+    <t xml:space="preserve"> {{说明}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1113,7 +1110,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>{{小时}}</t>
+      <t xml:space="preserve"> {{类别}}</t>
     </r>
     <r>
       <rPr>
@@ -1122,13 +1119,21 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>小时</t>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☑</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>至</t>
+      <t xml:space="preserve"> 自 </t>
     </r>
     <r>
       <rPr>
@@ -1138,13 +1143,13 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>{{至日期}} {{结束}}</t>
+      <t>{{起日期}} {{开始}}</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>自</t>
+      <t xml:space="preserve"> 至 </t>
     </r>
     <r>
       <rPr>
@@ -1154,11 +1159,14 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>{{起日期}} {{开始}}</t>
+      <t>{{至日期}} {{结束}}</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">共 </t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -1167,7 +1175,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>{{类别}}</t>
+      <t xml:space="preserve">{{小时}} </t>
     </r>
     <r>
       <rPr>
@@ -1176,15 +1184,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☑</t>
+      <t>小时</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1193,7 +1193,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1292,13 +1292,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="26"/>
-      <name val="新宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="18"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -1330,6 +1323,19 @@
       <b/>
       <sz val="20"/>
       <name val="仿宋"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="32"/>
+      <name val="新宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -1670,8 +1676,101 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1694,116 +1793,23 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2228,166 +2234,178 @@
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="7.5" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.5" customWidth="1"/>
-    <col min="10" max="10" width="13.375" customWidth="1"/>
-    <col min="11" max="12" width="7.5" customWidth="1"/>
+    <col min="1" max="1" width="9" style="54" customWidth="1"/>
+    <col min="2" max="2" width="9.5" customWidth="1"/>
+    <col min="3" max="3" width="7.5" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="9.5" customWidth="1"/>
+    <col min="6" max="6" width="7.5" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9.5" customWidth="1"/>
+    <col min="9" max="9" width="7.5" customWidth="1"/>
+    <col min="10" max="10" width="11.375" customWidth="1"/>
+    <col min="11" max="11" width="9.5" customWidth="1"/>
+    <col min="12" max="12" width="7.5" customWidth="1"/>
     <col min="13" max="13" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="50.25" customHeight="1" thickBot="1">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:13" ht="58.5" customHeight="1" thickBot="1">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-    </row>
-    <row r="2" spans="1:13" ht="54" customHeight="1">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+    </row>
+    <row r="2" spans="1:13" ht="57.95" customHeight="1">
+      <c r="A2" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="55" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="E2" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="25"/>
+      <c r="G2" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" s="26"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="K2" s="26"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="14"/>
+    </row>
+    <row r="3" spans="1:13" ht="57.95" customHeight="1">
+      <c r="A3" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="23"/>
+    </row>
+    <row r="4" spans="1:13" ht="57.95" customHeight="1">
+      <c r="A4" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="22"/>
+      <c r="F4" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="34"/>
+    </row>
+    <row r="5" spans="1:13" ht="57.95" customHeight="1">
+      <c r="A5" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="22"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="H5" s="22"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="K5" s="40"/>
+      <c r="L5" s="41"/>
+    </row>
+    <row r="6" spans="1:13" ht="66" customHeight="1" thickBot="1">
+      <c r="A6" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="43"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="43"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="43"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" s="57" t="s">
-        <v>114</v>
-      </c>
-      <c r="F2" s="58"/>
-      <c r="G2" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="H2" s="38"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="K2" s="38"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="22"/>
-    </row>
-    <row r="3" spans="1:13" ht="54" customHeight="1">
-      <c r="A3" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="23"/>
-    </row>
-    <row r="4" spans="1:13" ht="71.25" customHeight="1">
-      <c r="A4" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E4" s="28"/>
-      <c r="F4" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="23"/>
-    </row>
-    <row r="5" spans="1:13" ht="54" customHeight="1">
-      <c r="A5" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="K5" s="54"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="23"/>
-    </row>
-    <row r="6" spans="1:13" ht="66" customHeight="1" thickBot="1">
-      <c r="A6" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="49" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="47"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="51" t="s">
+      <c r="K6" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="K6" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="L6" s="52"/>
-      <c r="M6" s="23"/>
+      <c r="L6" s="45"/>
     </row>
     <row r="7" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:L5"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="D3:L3"/>
     <mergeCell ref="A1:L1"/>
@@ -2395,18 +2413,6 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="A7:L7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2426,18 +2432,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2491,29 +2497,29 @@
         <v>20</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.25" thickBot="1">
       <c r="A9" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.25" thickBot="1">
       <c r="A10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17.25" thickBot="1">
@@ -2529,10 +2535,10 @@
     </row>
     <row r="12" spans="1:3" ht="17.25" thickBot="1">
       <c r="A12" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>24</v>
@@ -2540,7 +2546,7 @@
     </row>
     <row r="13" spans="1:3" ht="17.25" thickBot="1">
       <c r="A13" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>25</v>
@@ -2557,7 +2563,7 @@
         <v>28</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17.25" thickBot="1">
@@ -2591,7 +2597,7 @@
     </row>
     <row r="18" spans="1:3" ht="17.25" thickBot="1">
       <c r="A18" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>36</v>
@@ -2623,11 +2629,11 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
       <c r="A22" s="1" t="s">
@@ -2642,7 +2648,7 @@
         <v>45</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="17.25" thickBot="1">
@@ -2694,11 +2700,11 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="51"/>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
       <c r="A31" s="1" t="s">
@@ -2788,98 +2794,98 @@
       <c r="C39" s="4"/>
     </row>
     <row r="40" spans="1:3" ht="16.5">
-      <c r="A40" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
+      <c r="A40" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" s="51"/>
+      <c r="C40" s="51"/>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A41" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B41" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="41.25" customHeight="1" thickBot="1">
       <c r="A42" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B42" s="12" t="s">
-        <v>95</v>
-      </c>
       <c r="C42" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B43" s="12" t="s">
-        <v>97</v>
-      </c>
       <c r="C43" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="33.75" thickBot="1">
       <c r="A44" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="33.75" thickBot="1">
       <c r="A45" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="17.25" thickBot="1">
       <c r="A46" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>100</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="33.75" thickBot="1">
       <c r="A47" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="33.75" thickBot="1">
       <c r="A48" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="16.5">
@@ -2893,28 +2899,28 @@
       <c r="A50">
         <v>1</v>
       </c>
-      <c r="B50" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C50" s="16"/>
+      <c r="B50" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="47"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <v>2</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="C51" s="16"/>
+      <c r="C51" s="47"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
         <v>3</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="C52" s="16"/>
+      <c r="C52" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB419F9-DA41-431B-BEFD-36CAE1C1687F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3293F8F-1C0B-4EAF-967F-5CD8758FAE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="121">
   <si>
     <t>请 假 单</t>
   </si>
@@ -1055,14 +1055,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>姓名：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>部门：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>职别：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1078,14 +1070,6 @@
     <t>如果“请假类别”为“其它”，请在“请假事由”中备注情况</t>
   </si>
   <si>
-    <t>{{{一级部门}}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{姓名}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>请假人:</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1103,62 +1087,103 @@
   </si>
   <si>
     <r>
+      <t>部门：</t>
+    </r>
+    <r>
       <rPr>
         <b/>
-        <sz val="20"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> {{类别}}</t>
-    </r>
-    <r>
-      <rPr>
         <sz val="18"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
+      <t>{{{一级部门}}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>姓名：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="18"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☑</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> 自 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>{{起日期}} {{开始}}</t>
+      <t>{{姓名}}</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t xml:space="preserve"> 至 </t>
-    </r>
-    <r>
       <rPr>
         <b/>
-        <sz val="20"/>
+        <sz val="16"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
+      <t xml:space="preserve"> {{类别}}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☑</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 自 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{{起日期}} {{开始}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
       <t>{{至日期}} {{结束}}</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1170,7 +1195,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="20"/>
+        <sz val="18"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
@@ -1193,7 +1218,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1310,19 +1335,7 @@
     </font>
     <font>
       <sz val="18"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <name val="仿宋"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -1338,6 +1351,31 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="仿宋"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="仿宋"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="仿宋"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1633,7 +1671,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1679,15 +1717,69 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1697,20 +1789,8 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1721,57 +1801,6 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1793,23 +1822,38 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2234,7 +2278,7 @@
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="54" customWidth="1"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
     <col min="3" max="3" width="7.5" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2250,155 +2294,153 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="58.5" customHeight="1" thickBot="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
     </row>
     <row r="2" spans="1:13" ht="57.95" customHeight="1">
       <c r="A2" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="51"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="H2" s="40"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="K2" s="40"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="14"/>
+    </row>
+    <row r="3" spans="1:13" ht="57.95" customHeight="1">
+      <c r="A3" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="37"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="E2" s="24" t="s">
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="56"/>
+    </row>
+    <row r="4" spans="1:13" ht="57.95" customHeight="1">
+      <c r="A4" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="58"/>
+      <c r="F4" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="29"/>
+    </row>
+    <row r="5" spans="1:13" ht="57.95" customHeight="1">
+      <c r="A5" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="55"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="H5" s="55"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="K5" s="34"/>
+      <c r="L5" s="35"/>
+    </row>
+    <row r="6" spans="1:13" ht="66" customHeight="1" thickBot="1">
+      <c r="A6" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="25"/>
-      <c r="G2" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="H2" s="26"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="K2" s="26"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="14"/>
-    </row>
-    <row r="3" spans="1:13" ht="57.95" customHeight="1">
-      <c r="A3" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="23"/>
-    </row>
-    <row r="4" spans="1:13" ht="57.95" customHeight="1">
-      <c r="A4" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="34"/>
-    </row>
-    <row r="5" spans="1:13" ht="57.95" customHeight="1">
-      <c r="A5" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="22"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="K5" s="40"/>
-      <c r="L5" s="41"/>
-    </row>
-    <row r="6" spans="1:13" ht="66" customHeight="1" thickBot="1">
-      <c r="A6" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" s="43"/>
+      <c r="E6" s="21"/>
       <c r="F6" s="16"/>
-      <c r="G6" s="44" t="s">
+      <c r="G6" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="43"/>
+      <c r="H6" s="21"/>
       <c r="I6" s="16"/>
       <c r="J6" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="K6" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="L6" s="45"/>
+        <v>111</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="L6" s="23"/>
     </row>
     <row r="7" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:L4"/>
@@ -2406,13 +2448,11 @@
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:L5"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:L3"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="A7:L7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2432,18 +2472,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2629,11 +2669,11 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A21" s="51" t="s">
+      <c r="A21" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="51"/>
-      <c r="C21" s="51"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
       <c r="A22" s="1" t="s">
@@ -2700,11 +2740,11 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
       <c r="A31" s="1" t="s">
@@ -2794,11 +2834,11 @@
       <c r="C39" s="4"/>
     </row>
     <row r="40" spans="1:3" ht="16.5">
-      <c r="A40" s="52" t="s">
+      <c r="A40" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="B40" s="51"/>
-      <c r="C40" s="51"/>
+      <c r="B40" s="48"/>
+      <c r="C40" s="48"/>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A41" s="11" t="s">
@@ -2899,28 +2939,28 @@
       <c r="A50">
         <v>1</v>
       </c>
-      <c r="B50" s="46" t="s">
+      <c r="B50" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C50" s="47"/>
+      <c r="C50" s="44"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <v>2</v>
       </c>
-      <c r="B51" s="47" t="s">
+      <c r="B51" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="C51" s="47"/>
+      <c r="C51" s="44"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
         <v>3</v>
       </c>
-      <c r="B52" s="47" t="s">
+      <c r="B52" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="C52" s="47"/>
+      <c r="C52" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3293F8F-1C0B-4EAF-967F-5CD8758FAE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2A3986-524E-4562-9937-657A898BFFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -32,18 +32,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="121">
-  <si>
-    <t>请 假 单</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="122">
   <si>
     <t>请假期间</t>
-  </si>
-  <si>
-    <t xml:space="preserve">总经理:　               </t>
-  </si>
-  <si>
-    <t>综合人事：</t>
   </si>
   <si>
     <t>注：三天以上假期，需总经理签核。</t>
@@ -1070,19 +1061,7 @@
     <t>如果“请假类别”为“其它”，请在“请假事由”中备注情况</t>
   </si>
   <si>
-    <t>请假人:</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{签名}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>部门经理：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> {{说明}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1119,6 +1098,34 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve"> 自 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{{起日期}} {{开始}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
       <rPr>
         <b/>
         <sz val="16"/>
@@ -1126,30 +1133,13 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> {{类别}}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☑</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> 自 </t>
+      <t>{{至日期}} {{结束}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">共 </t>
     </r>
     <r>
       <rPr>
@@ -1159,23 +1149,24 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>{{起日期}} {{开始}}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> 至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
+      <t xml:space="preserve">{{小时}} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
+      <t>小时</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{说明}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1184,33 +1175,51 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>{{至日期}} {{结束}}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">共 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
+      <t>{{类别}}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">{{小时}} </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>小时</t>
-    </r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☑</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>综合人事：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请假人：{{签名}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">总经理：　               </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">单号：{{单据号}}
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">打印时间：{{{打印时间}}}
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请 假 单</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1218,7 +1227,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1310,13 +1319,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="18"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -1332,12 +1334,6 @@
       <sz val="18"/>
       <name val="ˎ̥"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1377,6 +1373,12 @@
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="新宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1398,7 +1400,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1665,13 +1667,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1714,92 +1725,8 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1822,38 +1749,92 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2275,172 +2256,169 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="3" max="3" width="7.5" customWidth="1"/>
+    <col min="2" max="3" width="9.5" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="7.5" customWidth="1"/>
+    <col min="5" max="6" width="9.5" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="9.5" customWidth="1"/>
-    <col min="9" max="9" width="7.5" customWidth="1"/>
+    <col min="8" max="9" width="9.5" customWidth="1"/>
     <col min="10" max="10" width="11.375" customWidth="1"/>
-    <col min="11" max="11" width="9.5" customWidth="1"/>
-    <col min="12" max="12" width="7.5" customWidth="1"/>
-    <col min="13" max="13" width="2" customWidth="1"/>
+    <col min="11" max="12" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="58.5" customHeight="1" thickBot="1">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:12" ht="58.5" customHeight="1" thickBot="1">
+      <c r="A1" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+    </row>
+    <row r="2" spans="1:12" ht="57.95" customHeight="1">
+      <c r="A2" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="24"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="24"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="K2" s="24"/>
+      <c r="L2" s="27"/>
+    </row>
+    <row r="3" spans="1:12" ht="57.95" customHeight="1">
+      <c r="A3" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="29"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="33"/>
+    </row>
+    <row r="4" spans="1:12" ht="57.95" customHeight="1">
+      <c r="A4" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="38"/>
+      <c r="F4" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="40"/>
+    </row>
+    <row r="5" spans="1:12" ht="57.95" customHeight="1">
+      <c r="A5" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-    </row>
-    <row r="2" spans="1:13" ht="57.95" customHeight="1">
-      <c r="A2" s="53" t="s">
+      <c r="B5" s="35"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="32"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="32"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="K5" s="39"/>
+      <c r="L5" s="40"/>
+    </row>
+    <row r="6" spans="1:12" ht="93" customHeight="1" thickBot="1">
+      <c r="A6" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="45"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="H2" s="40"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="14"/>
-    </row>
-    <row r="3" spans="1:13" ht="57.95" customHeight="1">
-      <c r="A3" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="56"/>
-    </row>
-    <row r="4" spans="1:13" ht="57.95" customHeight="1">
-      <c r="A4" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="57" t="s">
+      <c r="H6" s="45"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="E4" s="58"/>
-      <c r="F4" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="29"/>
-    </row>
-    <row r="5" spans="1:13" ht="57.95" customHeight="1">
-      <c r="A5" s="30" t="s">
+      <c r="K6" s="45"/>
+      <c r="L6" s="48"/>
+    </row>
+    <row r="7" spans="1:12" ht="33.75" customHeight="1">
+      <c r="A7" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="H5" s="55"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="K5" s="34"/>
-      <c r="L5" s="35"/>
-    </row>
-    <row r="6" spans="1:13" ht="66" customHeight="1" thickBot="1">
-      <c r="A6" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="21"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="L6" s="23"/>
-    </row>
-    <row r="7" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A7" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:L3"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="21">
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A7:L7"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:L4"/>
@@ -2448,15 +2426,16 @@
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:L5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" scale="77" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="11" scale="71" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -2472,465 +2451,465 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
+      <c r="A1" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="47" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.25" thickBot="1">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.25" thickBot="1">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.25" thickBot="1">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.25" thickBot="1">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.25" thickBot="1">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.25" thickBot="1">
       <c r="A10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17.25" thickBot="1">
       <c r="A11" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17.25" thickBot="1">
       <c r="A12" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17.25" thickBot="1">
       <c r="A13" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="17.25" thickBot="1">
       <c r="A14" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17.25" thickBot="1">
       <c r="A15" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17.25" thickBot="1">
       <c r="A16" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3" ht="17.25" thickBot="1">
       <c r="A17" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" ht="17.25" thickBot="1">
       <c r="A18" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" thickBot="1">
       <c r="A19" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="17.25" thickBot="1">
       <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A21" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A21" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="48"/>
-      <c r="C21" s="48"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
       <c r="A22" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="17.25" thickBot="1">
       <c r="A24" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="17.25" thickBot="1">
       <c r="A25" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="17.25" thickBot="1">
       <c r="A26" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="17.25" thickBot="1">
       <c r="A27" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
       <c r="A28" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A30" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="48"/>
-      <c r="C30" s="48"/>
+      <c r="A30" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
       <c r="A31" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="17.25" thickBot="1">
       <c r="A33" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="17.25" thickBot="1">
       <c r="A34" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C34" s="4"/>
     </row>
     <row r="35" spans="1:3" ht="17.25" thickBot="1">
       <c r="A35" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C35" s="4"/>
     </row>
     <row r="36" spans="1:3" ht="17.25" thickBot="1">
       <c r="A36" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C36" s="4"/>
     </row>
     <row r="37" spans="1:3" ht="17.25" thickBot="1">
       <c r="A37" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C37" s="4"/>
     </row>
     <row r="38" spans="1:3" ht="17.25" thickBot="1">
       <c r="A38" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C38" s="4"/>
     </row>
     <row r="39" spans="1:3" ht="17.25" thickBot="1">
       <c r="A39" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C39" s="4"/>
     </row>
     <row r="40" spans="1:3" ht="16.5">
-      <c r="A40" s="49" t="s">
-        <v>90</v>
-      </c>
-      <c r="B40" s="48"/>
-      <c r="C40" s="48"/>
+      <c r="A40" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A41" s="11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="41.25" customHeight="1" thickBot="1">
       <c r="A42" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="33.75" thickBot="1">
       <c r="A44" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="33.75" thickBot="1">
       <c r="A45" s="11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="17.25" thickBot="1">
       <c r="A46" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="33.75" thickBot="1">
       <c r="A47" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="33.75" thickBot="1">
       <c r="A48" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="16.5">
       <c r="A49" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -2939,28 +2918,28 @@
       <c r="A50">
         <v>1</v>
       </c>
-      <c r="B50" s="43" t="s">
-        <v>103</v>
-      </c>
-      <c r="C50" s="44"/>
+      <c r="B50" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" s="16"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <v>2</v>
       </c>
-      <c r="B51" s="44" t="s">
-        <v>76</v>
-      </c>
-      <c r="C51" s="44"/>
+      <c r="B51" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="16"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
         <v>3</v>
       </c>
-      <c r="B52" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="C52" s="44"/>
+      <c r="B52" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2A3986-524E-4562-9937-657A898BFFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DC542A-03E5-4DCC-82BE-3D0EBB7241B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1725,9 +1725,81 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1749,92 +1821,20 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2270,154 +2270,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="58.5" customHeight="1" thickBot="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="22" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="49" t="s">
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
     </row>
     <row r="2" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26" t="s">
+      <c r="B2" s="35"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="24"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="26" t="s">
+      <c r="E2" s="35"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="H2" s="24"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="26" t="s">
+      <c r="H2" s="35"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="K2" s="24"/>
-      <c r="L2" s="27"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="38"/>
     </row>
     <row r="3" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="31" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
       <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="37" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39" t="s">
+      <c r="E4" s="22"/>
+      <c r="F4" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="40"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="24"/>
     </row>
     <row r="5" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="41" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="32"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="41" t="s">
+      <c r="E5" s="26"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="H5" s="32"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43" t="s">
+      <c r="H5" s="26"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="K5" s="39"/>
-      <c r="L5" s="40"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="24"/>
     </row>
     <row r="6" spans="1:12" ht="93" customHeight="1" thickBot="1">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="46" t="s">
+      <c r="B6" s="47"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="46" t="s">
+      <c r="E6" s="47"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49" t="s">
         <v>116</v>
       </c>
-      <c r="H6" s="45"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="46" t="s">
+      <c r="H6" s="47"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="K6" s="45"/>
-      <c r="L6" s="48"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="50"/>
     </row>
     <row r="7" spans="1:12" ht="33.75" customHeight="1">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:L1"/>
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:E4"/>
@@ -2426,6 +2419,13 @@
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:L5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="I1:L1"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="D3:L3"/>
     <mergeCell ref="D2:F2"/>
@@ -2451,18 +2451,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2648,11 +2648,11 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
       <c r="A22" s="1" t="s">
@@ -2719,11 +2719,11 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
       <c r="A31" s="1" t="s">
@@ -2813,11 +2813,11 @@
       <c r="C39" s="4"/>
     </row>
     <row r="40" spans="1:3" ht="16.5">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="44"/>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A41" s="11" t="s">
@@ -2918,28 +2918,28 @@
       <c r="A50">
         <v>1</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="16"/>
+      <c r="C50" s="40"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <v>2</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="C51" s="16"/>
+      <c r="C51" s="40"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
         <v>3</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="16"/>
+      <c r="C52" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DC542A-03E5-4DCC-82BE-3D0EBB7241B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A329BC-B1B0-4648-89FF-FA9C09AC550B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="123">
   <si>
     <t>请假期间</t>
   </si>
@@ -1059,10 +1059,6 @@
   </si>
   <si>
     <t>如果“请假类别”为“其它”，请在“请假事由”中备注情况</t>
-  </si>
-  <si>
-    <t>部门经理：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1197,18 +1193,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>综合人事：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请假人：{{签名}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">总经理：　               </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">单号：{{单据号}}
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1220,6 +1204,30 @@
   </si>
   <si>
     <t>请 假 单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+总经理：　               </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+部门经理：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+综合人事：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+请假人：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{签名}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1682,7 +1690,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1725,6 +1733,54 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1734,42 +1790,6 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1821,20 +1841,14 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2265,152 +2279,163 @@
     <col min="5" max="6" width="9.5" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="9" width="9.5" customWidth="1"/>
-    <col min="10" max="10" width="11.375" customWidth="1"/>
+    <col min="10" max="10" width="13.5" customWidth="1"/>
     <col min="11" max="12" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="58.5" customHeight="1" thickBot="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+    </row>
+    <row r="2" spans="1:12" ht="57.95" customHeight="1">
+      <c r="A2" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="39"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="H2" s="39"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="K2" s="39"/>
+      <c r="L2" s="42"/>
+    </row>
+    <row r="3" spans="1:12" ht="57.95" customHeight="1">
+      <c r="A3" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="34"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="37"/>
+    </row>
+    <row r="4" spans="1:12" ht="57.95" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="21"/>
+    </row>
+    <row r="5" spans="1:12" ht="57.95" customHeight="1">
+      <c r="A5" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="23"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="H5" s="23"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="K5" s="20"/>
+      <c r="L5" s="21"/>
+    </row>
+    <row r="6" spans="1:12" ht="93" customHeight="1" thickBot="1">
+      <c r="A6" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="27"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="14" t="s">
+      <c r="H6" s="27"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-    </row>
-    <row r="2" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A2" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" s="35"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="H2" s="35"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="K2" s="35"/>
-      <c r="L2" s="38"/>
-    </row>
-    <row r="3" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A3" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="33"/>
-    </row>
-    <row r="4" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A4" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="24"/>
-    </row>
-    <row r="5" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A5" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="E5" s="26"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="H5" s="26"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="K5" s="23"/>
-      <c r="L5" s="24"/>
-    </row>
-    <row r="6" spans="1:12" ht="93" customHeight="1" thickBot="1">
-      <c r="A6" s="46" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49" t="s">
-        <v>116</v>
-      </c>
-      <c r="H6" s="47"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="49" t="s">
-        <v>117</v>
-      </c>
-      <c r="K6" s="47"/>
-      <c r="L6" s="50"/>
+      <c r="K6" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="L6" s="52"/>
     </row>
     <row r="7" spans="1:12" ht="33.75" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:E4"/>
@@ -2421,21 +2446,12 @@
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G6:I6"/>
-    <mergeCell ref="J6:L6"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:L3"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="K6:L6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" scale="71" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="11" scale="70" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -2451,18 +2467,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2648,11 +2664,11 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
       <c r="A22" s="1" t="s">
@@ -2719,11 +2735,11 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A30" s="44" t="s">
+      <c r="A30" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="44"/>
-      <c r="C30" s="44"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
       <c r="A31" s="1" t="s">
@@ -2813,11 +2829,11 @@
       <c r="C39" s="4"/>
     </row>
     <row r="40" spans="1:3" ht="16.5">
-      <c r="A40" s="45" t="s">
+      <c r="A40" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="44"/>
-      <c r="C40" s="44"/>
+      <c r="B40" s="48"/>
+      <c r="C40" s="48"/>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A41" s="11" t="s">
@@ -2918,28 +2934,28 @@
       <c r="A50">
         <v>1</v>
       </c>
-      <c r="B50" s="39" t="s">
+      <c r="B50" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="40"/>
+      <c r="C50" s="44"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <v>2</v>
       </c>
-      <c r="B51" s="40" t="s">
+      <c r="B51" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="C51" s="40"/>
+      <c r="C51" s="44"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
         <v>3</v>
       </c>
-      <c r="B52" s="40" t="s">
+      <c r="B52" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="40"/>
+      <c r="C52" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A329BC-B1B0-4648-89FF-FA9C09AC550B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F885E6D6-5C17-498E-9539-FF5592DBFC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1733,6 +1733,51 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1760,9 +1805,6 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1781,45 +1823,6 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1841,14 +1844,11 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2284,124 +2284,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="58.5" customHeight="1" thickBot="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="30" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="32" t="s">
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="38" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="38" t="s">
+      <c r="E2" s="25"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="H2" s="39"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="38" t="s">
+      <c r="H2" s="25"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="K2" s="39"/>
-      <c r="L2" s="42"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="28"/>
     </row>
     <row r="3" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36" t="s">
+      <c r="B3" s="19"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="37"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="23"/>
     </row>
     <row r="4" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="18" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="20" t="s">
+      <c r="E4" s="34"/>
+      <c r="F4" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="21"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="36"/>
     </row>
     <row r="5" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="22" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="22" t="s">
+      <c r="E5" s="22"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="25" t="s">
+      <c r="H5" s="22"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="21"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="36"/>
     </row>
     <row r="6" spans="1:12" ht="93" customHeight="1" thickBot="1">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="26" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="26" t="s">
+      <c r="E6" s="41"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="H6" s="27"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="50" t="s">
+      <c r="H6" s="41"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="14" t="s">
         <v>121</v>
       </c>
       <c r="K6" s="51" t="s">
@@ -2410,32 +2410,23 @@
       <c r="L6" s="52"/>
     </row>
     <row r="7" spans="1:12" ht="33.75" customHeight="1">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:L3"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:E4"/>
@@ -2448,6 +2439,15 @@
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="K6:L6"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2467,18 +2467,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2664,11 +2664,11 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A21" s="48" t="s">
+      <c r="A21" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="48"/>
-      <c r="C21" s="48"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
       <c r="A22" s="1" t="s">
@@ -2735,11 +2735,11 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A30" s="48" t="s">
+      <c r="A30" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="48"/>
-      <c r="C30" s="48"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="49"/>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
       <c r="A31" s="1" t="s">
@@ -2829,11 +2829,11 @@
       <c r="C39" s="4"/>
     </row>
     <row r="40" spans="1:3" ht="16.5">
-      <c r="A40" s="49" t="s">
+      <c r="A40" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="48"/>
-      <c r="C40" s="48"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="49"/>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A41" s="11" t="s">
@@ -2934,28 +2934,28 @@
       <c r="A50">
         <v>1</v>
       </c>
-      <c r="B50" s="43" t="s">
+      <c r="B50" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="44"/>
+      <c r="C50" s="45"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
         <v>2</v>
       </c>
-      <c r="B51" s="44" t="s">
+      <c r="B51" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="C51" s="44"/>
+      <c r="C51" s="45"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
         <v>3</v>
       </c>
-      <c r="B52" s="44" t="s">
+      <c r="B52" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="44"/>
+      <c r="C52" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F885E6D6-5C17-498E-9539-FF5592DBFC30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C063A4-0006-45F3-8067-A2D0BB440C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="129">
   <si>
     <t>请假期间</t>
   </si>
@@ -743,14 +743,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>多日请假的起日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多日请假的至日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MM-DD</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1044,14 +1036,6 @@
       <t>}}</t>
     </r>
     <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>职别：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>代理人：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>请假事由</t>
@@ -1094,7 +1078,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve"> 自 </t>
+      <t xml:space="preserve">共 </t>
     </r>
     <r>
       <rPr>
@@ -1104,13 +1088,236 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
+      <t xml:space="preserve">{{小时}} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小时</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{说明}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">单号：{{单据号}}
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">打印时间：{{{打印时间}}}
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请 假 单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{签名}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{{类别}}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☑</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请假才有</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="4"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代理人}} </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请假才有，多日请假的起日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请假才有，多日请假的至日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岗位职别</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>职别：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{{岗位职别}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>代理人：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">{{代理人}} </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+　               </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部门经理：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>综合人事：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请假人：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总经理：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岗位职别</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">}}} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>也能用</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">自 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
       <t>{{起日期}} {{开始}}</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t xml:space="preserve"> 至</t>
+      <t>至</t>
     </r>
     <r>
       <rPr>
@@ -1131,103 +1338,6 @@
       </rPr>
       <t>{{至日期}} {{结束}}</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">共 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">{{小时}} </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>小时</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{说明}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>{{类别}}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☑</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">单号：{{单据号}}
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">打印时间：{{{打印时间}}}
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请 假 单</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-总经理：　               </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-部门经理：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-综合人事：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-请假人：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{签名}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1235,7 +1345,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1377,15 +1487,28 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="12"/>
+      <name val="新宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="新宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <b/>
+      <sz val="10"/>
+      <color theme="4"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="4"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1408,7 +1531,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1563,32 +1686,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1634,43 +1731,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1684,13 +1744,95 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1733,16 +1875,43 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1757,98 +1926,104 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1873,13 +2048,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1927,13 +2102,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>428625</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2270,7 +2445,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -2279,166 +2454,177 @@
     <col min="5" max="6" width="9.5" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="9" width="9.5" customWidth="1"/>
-    <col min="10" max="10" width="13.5" customWidth="1"/>
-    <col min="11" max="12" width="9.5" customWidth="1"/>
+    <col min="10" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="58.5" customHeight="1" thickBot="1">
-      <c r="A1" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="A1" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
     </row>
     <row r="2" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A2" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="24" t="s">
+      <c r="A2" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="H2" s="25"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="K2" s="25"/>
-      <c r="L2" s="28"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="H2" s="33"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="K2" s="33"/>
+      <c r="L2" s="36"/>
     </row>
     <row r="3" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="31"/>
+    </row>
+    <row r="4" spans="1:12" ht="57.95" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="21"/>
+      <c r="F4" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="19"/>
+    </row>
+    <row r="5" spans="1:12" ht="57.95" customHeight="1">
+      <c r="A5" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="21"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="21"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="23"/>
-    </row>
-    <row r="4" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A4" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="34"/>
-      <c r="F4" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="36"/>
-    </row>
-    <row r="5" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A5" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="22"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="37" t="s">
+      <c r="K5" s="18"/>
+      <c r="L5" s="19"/>
+    </row>
+    <row r="6" spans="1:12" ht="38.25" customHeight="1">
+      <c r="A6" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="54"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="55"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="H6" s="55"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="K6" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="K5" s="35"/>
-      <c r="L5" s="36"/>
-    </row>
-    <row r="6" spans="1:12" ht="93" customHeight="1" thickBot="1">
-      <c r="A6" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="E6" s="41"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="40" t="s">
+      <c r="L6" s="63"/>
+    </row>
+    <row r="7" spans="1:12" ht="38.25" customHeight="1" thickBot="1">
+      <c r="A7" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="H6" s="41"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="14" t="s">
+      <c r="B7" s="50"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="K6" s="51" t="s">
-        <v>122</v>
-      </c>
-      <c r="L6" s="52"/>
-    </row>
-    <row r="7" spans="1:12" ht="33.75" customHeight="1">
-      <c r="A7" s="29" t="s">
+      <c r="E7" s="50"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="H7" s="50"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="K7" s="61"/>
+      <c r="L7" s="60"/>
+    </row>
+    <row r="8" spans="1:12" ht="33.75" customHeight="1">
+      <c r="A8" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="K6:L6"/>
+  <mergeCells count="24">
+    <mergeCell ref="K6:K7"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="I1:L1"/>
@@ -2448,6 +2634,20 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G6:I6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2458,7 +2658,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D308FF08-C618-4E02-BF80-7C3D53995006}">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.375" bestFit="1" customWidth="1"/>
@@ -2467,18 +2667,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2532,29 +2732,29 @@
         <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="48" t="s">
         <v>80</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="10" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="48" t="s">
         <v>81</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17.25" thickBot="1">
@@ -2598,7 +2798,7 @@
         <v>25</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17.25" thickBot="1">
@@ -2632,7 +2832,7 @@
     </row>
     <row r="18" spans="1:3" ht="17.25" thickBot="1">
       <c r="A18" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>33</v>
@@ -2664,309 +2864,327 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="45"/>
+    </row>
+    <row r="22" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A22" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
-    </row>
-    <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="1" t="s">
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+    </row>
+    <row r="23" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A23" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="17.25" thickBot="1">
       <c r="A24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="17.25" thickBot="1">
       <c r="A25" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="17.25" thickBot="1">
       <c r="A26" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="17.25" thickBot="1">
       <c r="A27" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" thickBot="1">
       <c r="A28" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="17.25" thickBot="1">
       <c r="A29" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A30" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B30" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A30" s="49" t="s">
+    <row r="31" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A31" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="49"/>
-      <c r="C30" s="49"/>
-    </row>
-    <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="1" t="s">
+      <c r="B31" s="42"/>
+      <c r="C31" s="42"/>
+    </row>
+    <row r="32" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A32" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="17.25" thickBot="1">
       <c r="A33" s="3" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="17.25" thickBot="1">
       <c r="A34" s="3" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="35" spans="1:3" ht="17.25" thickBot="1">
       <c r="A35" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C35" s="4"/>
     </row>
     <row r="36" spans="1:3" ht="17.25" thickBot="1">
       <c r="A36" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C36" s="4"/>
     </row>
     <row r="37" spans="1:3" ht="17.25" thickBot="1">
       <c r="A37" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C37" s="4"/>
     </row>
     <row r="38" spans="1:3" ht="17.25" thickBot="1">
       <c r="A38" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C38" s="4"/>
     </row>
     <row r="39" spans="1:3" ht="17.25" thickBot="1">
       <c r="A39" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="4"/>
+    </row>
+    <row r="40" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A40" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B40" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C39" s="4"/>
-    </row>
-    <row r="40" spans="1:3" ht="16.5">
-      <c r="A40" s="50" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" s="49"/>
-      <c r="C40" s="49"/>
-    </row>
-    <row r="41" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A41" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="41.25" customHeight="1" thickBot="1">
-      <c r="A42" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>89</v>
-      </c>
+      <c r="C40" s="4"/>
+    </row>
+    <row r="41" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A41" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="B41" s="44"/>
+      <c r="C41" s="45" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="16.5">
+      <c r="A42" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" s="42"/>
+      <c r="C42" s="42"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="41.25" customHeight="1" thickBot="1">
+      <c r="A44" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A45" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="33.75" thickBot="1">
+      <c r="A46" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="33.75" thickBot="1">
-      <c r="A44" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="33.75" thickBot="1">
-      <c r="A45" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A46" s="11" t="s">
-        <v>96</v>
-      </c>
       <c r="B46" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>97</v>
+        <v>91</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="33.75" thickBot="1">
       <c r="A47" s="11" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A48" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="33.75" thickBot="1">
+      <c r="A49" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="33.75" thickBot="1">
+      <c r="A50" s="11" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" ht="33.75" thickBot="1">
-      <c r="A48" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="16.5">
-      <c r="A49" s="6" t="s">
+      <c r="B50" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="16.5">
+      <c r="A51" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50">
-        <v>1</v>
-      </c>
-      <c r="B50" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="C50" s="45"/>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51">
-        <v>2</v>
-      </c>
-      <c r="B51" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="C51" s="45"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
+        <v>1</v>
+      </c>
+      <c r="B52" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" s="38"/>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
+        <v>2</v>
+      </c>
+      <c r="B53" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" s="38"/>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
         <v>3</v>
       </c>
-      <c r="B52" s="45" t="s">
+      <c r="B54" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="45"/>
+      <c r="C54" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
     <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A42:C42"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C063A4-0006-45F3-8067-A2D0BB440C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B519AC-9DFC-4AD4-91FA-0E23644B8CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1106,16 +1106,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">单号：{{单据号}}
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">打印时间：{{{打印时间}}}
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>请 假 单</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1338,6 +1328,14 @@
       </rPr>
       <t>{{至日期}} {{结束}}</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单号：{{单据号}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打印时间：{{{打印日期}}} {{{打印时间}}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1674,13 +1672,51 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1690,10 +1726,8 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1703,33 +1737,36 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1739,38 +1776,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1781,7 +1787,7 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1792,7 +1798,7 @@
       </left>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1803,27 +1809,9 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1832,7 +1820,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1875,6 +1863,54 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1887,62 +1923,47 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1965,65 +1986,35 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2048,13 +2039,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2102,13 +2093,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>428625</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2445,7 +2436,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -2454,200 +2445,215 @@
     <col min="5" max="6" width="9.5" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="9" width="9.5" customWidth="1"/>
-    <col min="10" max="11" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="5.5" customWidth="1"/>
+    <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="11" max="11" width="12.5" customWidth="1"/>
+    <col min="12" max="12" width="6.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="58.5" customHeight="1" thickBot="1">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:12" ht="58.5" customHeight="1">
+      <c r="A1" s="57" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="59" t="s">
+        <v>127</v>
+      </c>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+    </row>
+    <row r="2" spans="1:12" ht="7.5" customHeight="1" thickBot="1">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" ht="57.95" customHeight="1">
+      <c r="A3" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" s="61"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63" t="s">
+        <v>116</v>
+      </c>
+      <c r="H3" s="61"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="K3" s="61"/>
+      <c r="L3" s="64"/>
+    </row>
+    <row r="4" spans="1:12" ht="57.95" customHeight="1">
+      <c r="A4" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="29"/>
+    </row>
+    <row r="5" spans="1:12" ht="57.95" customHeight="1">
+      <c r="A5" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="32"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="28"/>
+      <c r="F5" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="36"/>
+    </row>
+    <row r="6" spans="1:12" ht="57.95" customHeight="1">
+      <c r="A6" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" s="28"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="H6" s="28"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="K6" s="35"/>
+      <c r="L6" s="36"/>
+    </row>
+    <row r="7" spans="1:12" ht="38.25" customHeight="1">
+      <c r="A7" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="44"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="46"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="H7" s="46"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="K7" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-    </row>
-    <row r="2" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A2" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="32" t="s">
+      <c r="L7" s="22"/>
+    </row>
+    <row r="8" spans="1:12" ht="38.25" customHeight="1" thickBot="1">
+      <c r="A8" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="H2" s="33"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="32" t="s">
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="K2" s="33"/>
-      <c r="L2" s="36"/>
-    </row>
-    <row r="3" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A3" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="31"/>
-    </row>
-    <row r="4" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A4" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" s="21"/>
-      <c r="F4" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="19"/>
-    </row>
-    <row r="5" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A5" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="K5" s="18"/>
-      <c r="L5" s="19"/>
-    </row>
-    <row r="6" spans="1:12" ht="38.25" customHeight="1">
-      <c r="A6" s="58" t="s">
-        <v>125</v>
-      </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="55" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="55"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="55" t="s">
-        <v>123</v>
-      </c>
-      <c r="H6" s="55"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="59" t="s">
-        <v>124</v>
-      </c>
-      <c r="K6" s="62" t="s">
-        <v>111</v>
-      </c>
-      <c r="L6" s="63"/>
-    </row>
-    <row r="7" spans="1:12" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A7" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="E7" s="50"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="H7" s="50"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="K7" s="61"/>
-      <c r="L7" s="60"/>
-    </row>
-    <row r="8" spans="1:12" ht="33.75" customHeight="1">
-      <c r="A8" s="14" t="s">
+      <c r="E8" s="40"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="40"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="K8" s="56"/>
+      <c r="L8" s="21"/>
+    </row>
+    <row r="9" spans="1:12" ht="33.75" customHeight="1">
+      <c r="A9" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:L3"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="A9:L9"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:L5"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:L4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="E1:H2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2667,18 +2673,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2736,22 +2742,22 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="18" t="s">
         <v>80</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="18" t="s">
         <v>81</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>82</v>
@@ -2864,20 +2870,20 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A21" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" s="45"/>
+      <c r="A21" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="16"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="42"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2944,11 +2950,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="42"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3038,20 +3044,20 @@
       <c r="C40" s="4"/>
     </row>
     <row r="41" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A41" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="B41" s="44"/>
-      <c r="C41" s="45" t="s">
-        <v>126</v>
+      <c r="A41" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" s="11"/>
+      <c r="C41" s="16" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="43" t="s">
+      <c r="A42" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="42"/>
-      <c r="C42" s="42"/>
+      <c r="B42" s="53"/>
+      <c r="C42" s="53"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3152,28 +3158,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="37" t="s">
+      <c r="B52" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="38"/>
+      <c r="C52" s="49"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="38" t="s">
+      <c r="B53" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="38"/>
+      <c r="C53" s="49"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="38" t="s">
+      <c r="B54" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="38"/>
+      <c r="C54" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B519AC-9DFC-4AD4-91FA-0E23644B8CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E147331-48EE-4315-B970-30DD88B07A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1045,79 +1045,208 @@
     <t>如果“请假类别”为“其它”，请在“请假事由”中备注情况</t>
   </si>
   <si>
-    <r>
-      <t>部门：</t>
+    <t>{{说明}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请 假 单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{签名}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请假才有</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{</t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="18"/>
+        <sz val="10"/>
+        <color theme="4"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">代理人}} </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请假才有，多日请假的起日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请假才有，多日请假的至日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岗位职别</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+　               </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部门经理：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>综合人事：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请假人：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总经理：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岗位职别</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">}}} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>也能用</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单号：{{单据号}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打印时间：{{{打印日期}}} {{{打印时间}}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>姓名：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>{{{一级部门}}}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>姓名：</t>
+      <t>{{姓名}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>部门：</t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="18"/>
+        <sz val="12"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>{{姓名}}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">共 </t>
+      <t>{{{一级部门}}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>职别：</t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="18"/>
+        <sz val="12"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">{{小时}} </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
+      <t>{{岗位职别}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>代理人：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>小时</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{说明}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请 假 单</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{签名}}</t>
+      <t xml:space="preserve">{{代理人}} </t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="18"/>
+        <sz val="12"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
@@ -1126,7 +1255,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="18"/>
+        <sz val="12"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
@@ -1135,7 +1264,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="18"/>
+        <sz val="12"/>
         <rFont val="Segoe UI Symbol"/>
         <family val="2"/>
       </rPr>
@@ -1144,198 +1273,60 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>请假才有</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{</t>
+    <r>
+      <t xml:space="preserve">自 </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="10"/>
-        <color theme="4"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">代理人}} </t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请假才有，多日请假的起日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请假才有，多日请假的至日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>岗位职别</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>}}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>职别：</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
+        <sz val="12"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>{{岗位职别}}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>代理人：</t>
+      <t>{{起日期}} {{开始}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">至 </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="18"/>
+        <sz val="12"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">{{代理人}} </t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-　               </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>部门经理：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>综合人事：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请假人：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>总经理：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>岗位职别</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">}}} </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>也能用</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">自 </t>
+      <t>{{至日期}} {{结束}}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">共 </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="18"/>
+        <sz val="12"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>{{起日期}} {{开始}}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
+      <t xml:space="preserve">{{小时}} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <rFont val="仿宋"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>{{至日期}} {{结束}}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单号：{{单据号}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打印时间：{{{打印日期}}} {{{打印时间}}}</t>
+      <t>小时</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1343,7 +1334,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1435,65 +1426,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="18"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <name val="仿宋"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <name val="ˎ̥"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="32"/>
-      <name val="新宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <name val="仿宋"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <name val="仿宋"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <name val="仿宋"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="新宋体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1506,6 +1442,54 @@
       <sz val="10"/>
       <color theme="4"/>
       <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="新宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <name val="新宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="仿宋"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="仿宋"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="ˎ̥"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1866,104 +1850,17 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1986,35 +1883,122 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2433,184 +2417,181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD1811D-72BB-4F54-B90A-4D27DF8394AD}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="3" width="9.5" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="6" width="9.5" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="9" width="9.5" customWidth="1"/>
-    <col min="10" max="10" width="13.5" customWidth="1"/>
-    <col min="11" max="11" width="12.5" customWidth="1"/>
-    <col min="12" max="12" width="6.5" customWidth="1"/>
+    <col min="1" max="2" width="6.625" customWidth="1"/>
+    <col min="3" max="3" width="6.5" customWidth="1"/>
+    <col min="4" max="5" width="6.625" customWidth="1"/>
+    <col min="6" max="6" width="6.5" customWidth="1"/>
+    <col min="7" max="8" width="6.625" customWidth="1"/>
+    <col min="9" max="9" width="6.5" customWidth="1"/>
+    <col min="10" max="10" width="9.625" customWidth="1"/>
+    <col min="11" max="11" width="8.625" customWidth="1"/>
+    <col min="12" max="12" width="4.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="58.5" customHeight="1">
-      <c r="A1" s="57" t="s">
-        <v>128</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="58" t="s">
-        <v>108</v>
-      </c>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="59" t="s">
-        <v>127</v>
-      </c>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
+    <row r="1" spans="1:12" ht="40.5" customHeight="1">
+      <c r="A1" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
     </row>
     <row r="2" spans="1:12" ht="7.5" customHeight="1" thickBot="1">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
     </row>
-    <row r="3" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A3" s="60" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" s="61"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="63" t="s">
+    <row r="3" spans="1:12" ht="38.1" customHeight="1">
+      <c r="A3" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="32"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" s="32"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="K3" s="32"/>
+      <c r="L3" s="35"/>
+    </row>
+    <row r="4" spans="1:12" ht="38.1" customHeight="1">
+      <c r="A4" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="37"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="E3" s="61"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63" t="s">
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="41"/>
+    </row>
+    <row r="5" spans="1:12" ht="38.1" customHeight="1">
+      <c r="A5" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="43"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="40"/>
+      <c r="F5" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="47"/>
+    </row>
+    <row r="6" spans="1:12" ht="38.1" customHeight="1">
+      <c r="A6" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="43"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" s="40"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="H6" s="40"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="K6" s="46"/>
+      <c r="L6" s="47"/>
+    </row>
+    <row r="7" spans="1:12" ht="30.75" customHeight="1">
+      <c r="A7" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="51"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="53"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="53" t="s">
+        <v>115</v>
+      </c>
+      <c r="H7" s="53"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="63" t="s">
-        <v>117</v>
-      </c>
-      <c r="K3" s="61"/>
-      <c r="L3" s="64"/>
-    </row>
-    <row r="4" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A4" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="29"/>
-    </row>
-    <row r="5" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A5" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="36"/>
-    </row>
-    <row r="6" spans="1:12" ht="57.95" customHeight="1">
-      <c r="A6" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="H6" s="28"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="38" t="s">
+      <c r="K7" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="K6" s="35"/>
-      <c r="L6" s="36"/>
-    </row>
-    <row r="7" spans="1:12" ht="38.25" customHeight="1">
-      <c r="A7" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" s="46"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="H7" s="46"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="K7" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="L7" s="22"/>
-    </row>
-    <row r="8" spans="1:12" ht="38.25" customHeight="1" thickBot="1">
-      <c r="A8" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8" s="40"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="H8" s="40"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="K8" s="56"/>
-      <c r="L8" s="21"/>
+      <c r="L7" s="56"/>
+    </row>
+    <row r="8" spans="1:12" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A8" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="58"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="60" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="58"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="60" t="s">
+        <v>113</v>
+      </c>
+      <c r="H8" s="58"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="61" t="s">
+        <v>113</v>
+      </c>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
     </row>
     <row r="9" spans="1:12" ht="33.75" customHeight="1">
       <c r="A9" s="30" t="s">
@@ -2630,6 +2611,15 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:L4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="E1:H2"/>
     <mergeCell ref="A9:L9"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
@@ -2645,19 +2635,10 @@
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="K7:K8"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:L4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="E1:H2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" scale="70" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="11" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -2673,18 +2654,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2746,7 +2727,7 @@
         <v>80</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>82</v>
@@ -2757,7 +2738,7 @@
         <v>81</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>82</v>
@@ -2871,19 +2852,19 @@
     </row>
     <row r="21" spans="1:3" ht="17.25" thickBot="1">
       <c r="A21" s="17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C21" s="16"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2950,11 +2931,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="53"/>
-      <c r="C31" s="53"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3045,19 +3026,19 @@
     </row>
     <row r="41" spans="1:3" ht="17.25" thickBot="1">
       <c r="A41" s="11" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B41" s="11"/>
       <c r="C41" s="16" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="54" t="s">
+      <c r="A42" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="53"/>
-      <c r="C42" s="53"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3158,28 +3139,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="48" t="s">
+      <c r="B52" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="49"/>
+      <c r="C52" s="20"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="49" t="s">
+      <c r="B53" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="49"/>
+      <c r="C53" s="20"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="49" t="s">
+      <c r="B54" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="49"/>
+      <c r="C54" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E147331-48EE-4315-B970-30DD88B07A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F377311-3974-45E2-89B4-4FE0D674904D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="129">
   <si>
     <t>请假期间</t>
   </si>
@@ -1862,6 +1862,105 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1883,122 +1982,23 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2432,194 +2432,183 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="40.5" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="28" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="27" t="s">
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
     </row>
     <row r="2" spans="1:12" ht="7.5" customHeight="1" thickBot="1">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
     </row>
     <row r="3" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="32"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="34" t="s">
+      <c r="E3" s="30"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="34" t="s">
+      <c r="H3" s="30"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="K3" s="32"/>
-      <c r="L3" s="35"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="33"/>
     </row>
     <row r="4" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="39" t="s">
+      <c r="B4" s="24"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="41"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="28"/>
     </row>
     <row r="5" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="45" t="s">
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="40"/>
-      <c r="F5" s="46" t="s">
+      <c r="E5" s="27"/>
+      <c r="F5" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="47"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="40"/>
     </row>
     <row r="6" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="45" t="s">
+      <c r="B6" s="36"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="40"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="45" t="s">
+      <c r="E6" s="27"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="H6" s="40"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="49" t="s">
+      <c r="H6" s="27"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="K6" s="46"/>
-      <c r="L6" s="47"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="1:12" ht="30.75" customHeight="1">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="53" t="s">
+      <c r="B7" s="48"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="53"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="53" t="s">
+      <c r="E7" s="50"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="53"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="64" t="s">
+      <c r="H7" s="50"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="K7" s="55" t="s">
+      <c r="K7" s="59"/>
+      <c r="L7" s="19"/>
+    </row>
+    <row r="8" spans="1:12" ht="31.5" customHeight="1" thickBot="1">
+      <c r="A8" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="44"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="44"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="H8" s="44"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="L7" s="56"/>
-    </row>
-    <row r="8" spans="1:12" ht="31.5" customHeight="1" thickBot="1">
-      <c r="A8" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="60" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="58"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="60" t="s">
-        <v>113</v>
-      </c>
-      <c r="H8" s="58"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="61" t="s">
-        <v>113</v>
-      </c>
-      <c r="K8" s="62"/>
-      <c r="L8" s="63"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="62"/>
     </row>
     <row r="9" spans="1:12" ht="33.75" customHeight="1">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:L4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="E1:H2"/>
     <mergeCell ref="A9:L9"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
@@ -2634,7 +2623,16 @@
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:L4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="E1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2654,18 +2652,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2860,11 +2858,11 @@
       <c r="C21" s="16"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="57"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2931,11 +2929,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="57"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3034,11 +3032,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="58" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3139,28 +3137,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="19" t="s">
+      <c r="B52" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="20"/>
+      <c r="C52" s="53"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="20" t="s">
+      <c r="B53" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="20"/>
+      <c r="C53" s="53"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="20" t="s">
+      <c r="B54" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="20"/>
+      <c r="C54" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F377311-3974-45E2-89B4-4FE0D674904D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F0DBEB-55A8-4B9A-9092-78A008CB6A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="127">
   <si>
     <t>请假期间</t>
   </si>
@@ -1284,12 +1284,15 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>{{起日期}} {{开始}}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
+      <t xml:space="preserve">{{起日期}} {{开始}} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">至 </t>
     </r>
     <r>
@@ -1302,11 +1305,14 @@
       </rPr>
       <t>{{至日期}} {{结束}}</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">共 </t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  共 </t>
     </r>
     <r>
       <rPr>
@@ -1316,7 +1322,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">{{小时}} </t>
+      <t>{{小时}}</t>
     </r>
     <r>
       <rPr>
@@ -1325,7 +1331,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>小时</t>
+      <t xml:space="preserve"> 小时</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1804,7 +1810,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1868,6 +1874,72 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1886,9 +1958,6 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1907,59 +1976,8 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1981,24 +1999,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2432,198 +2432,180 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="40.5" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="64" t="s">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="22" t="s">
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
     </row>
     <row r="2" spans="1:12" ht="7.5" customHeight="1" thickBot="1">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
     </row>
     <row r="3" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="29" t="s">
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="29" t="s">
+      <c r="E3" s="51"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="29" t="s">
+      <c r="H3" s="51"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="K3" s="30"/>
-      <c r="L3" s="33"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="54"/>
     </row>
     <row r="4" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26" t="s">
+      <c r="B4" s="46"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="49"/>
     </row>
     <row r="5" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="38" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="39" t="s">
+      <c r="E5" s="28"/>
+      <c r="F5" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="40"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30"/>
     </row>
     <row r="6" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="38" t="s">
+      <c r="B6" s="25"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="H6" s="27"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="K6" s="39"/>
-      <c r="L6" s="40"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="49"/>
     </row>
     <row r="7" spans="1:12" ht="30.75" customHeight="1">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="50" t="s">
+      <c r="B7" s="36"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="50"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="50" t="s">
+      <c r="E7" s="38"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="50"/>
-      <c r="I7" s="51"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="39"/>
       <c r="J7" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="K7" s="59"/>
+      <c r="K7" s="21"/>
       <c r="L7" s="19"/>
     </row>
     <row r="8" spans="1:12" ht="31.5" customHeight="1" thickBot="1">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="43" t="s">
+      <c r="B8" s="32"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="43" t="s">
+      <c r="E8" s="32"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="H8" s="44"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="60" t="s">
+      <c r="H8" s="32"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="K8" s="61"/>
-      <c r="L8" s="62"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="42"/>
     </row>
     <row r="9" spans="1:12" ht="33.75" customHeight="1">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J8:L8"/>
+  <mergeCells count="22">
+    <mergeCell ref="D6:L6"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="A4:C4"/>
@@ -2633,6 +2615,18 @@
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="E1:H1"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J8:L8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2652,18 +2646,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2858,11 +2852,11 @@
       <c r="C21" s="16"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="57"/>
-      <c r="C22" s="57"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2929,11 +2923,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="57"/>
-      <c r="C31" s="57"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="61"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3032,11 +3026,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="58" t="s">
+      <c r="A42" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="57"/>
-      <c r="C42" s="57"/>
+      <c r="B42" s="61"/>
+      <c r="C42" s="61"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3137,28 +3131,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="52" t="s">
+      <c r="B52" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="53"/>
+      <c r="C52" s="57"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="53" t="s">
+      <c r="B53" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="53"/>
+      <c r="C53" s="57"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="53" t="s">
+      <c r="B54" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="53"/>
+      <c r="C54" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F0DBEB-55A8-4B9A-9092-78A008CB6A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C283638-C8E3-412A-A4E4-B3752D34A34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1171,14 +1171,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>单号：{{单据号}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打印时间：{{{打印日期}}} {{{打印时间}}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>姓名：</t>
     </r>
@@ -1334,13 +1326,19 @@
       <t xml:space="preserve"> 小时</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打印时间：{{{打印日期}}} {{{打印时间}}}</t>
+  </si>
+  <si>
+    <t>单号：{{单据号}}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1432,12 +1430,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="新宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color theme="4"/>
@@ -1458,13 +1450,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="新宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="26"/>
       <name val="新宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1498,6 +1483,13 @@
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="新宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1519,7 +1511,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1804,13 +1796,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1853,131 +1856,110 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1999,6 +1981,24 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2431,190 +2431,180 @@
     <col min="12" max="12" width="4.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="40.5" customHeight="1">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:12" ht="32.25" customHeight="1">
+      <c r="A1" s="20"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+    </row>
+    <row r="2" spans="1:12" ht="18.75" customHeight="1" thickBot="1">
+      <c r="A2" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+    </row>
+    <row r="3" spans="1:12" ht="38.1" customHeight="1">
+      <c r="A3" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="27"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-    </row>
-    <row r="2" spans="1:12" ht="7.5" customHeight="1" thickBot="1">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A3" s="53" t="s">
+      <c r="E3" s="27"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="50" t="s">
+      <c r="H3" s="27"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="50" t="s">
+      <c r="K3" s="27"/>
+      <c r="L3" s="30"/>
+    </row>
+    <row r="4" spans="1:12" ht="38.1" customHeight="1">
+      <c r="A4" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="23"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="19"/>
+    </row>
+    <row r="5" spans="1:12" ht="38.1" customHeight="1">
+      <c r="A5" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="33"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="51"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="50" t="s">
+      <c r="E5" s="18"/>
+      <c r="F5" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="36"/>
+    </row>
+    <row r="6" spans="1:12" ht="38.1" customHeight="1">
+      <c r="A6" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="K3" s="51"/>
-      <c r="L3" s="54"/>
-    </row>
-    <row r="4" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A4" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="48" t="s">
-        <v>104</v>
-      </c>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="49"/>
-    </row>
-    <row r="5" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A5" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="30"/>
-    </row>
-    <row r="6" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A6" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="49"/>
-    </row>
-    <row r="7" spans="1:12" ht="30.75" customHeight="1">
-      <c r="A7" s="35" t="s">
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="19"/>
+    </row>
+    <row r="7" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A7" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="38" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="38"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="38" t="s">
+      <c r="E7" s="44"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="20" t="s">
+      <c r="H7" s="44"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="57" t="s">
         <v>116</v>
       </c>
-      <c r="K7" s="21"/>
-      <c r="L7" s="19"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="59"/>
     </row>
     <row r="8" spans="1:12" ht="31.5" customHeight="1" thickBot="1">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="31" t="s">
+      <c r="B8" s="38"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="31" t="s">
+      <c r="E8" s="38"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="H8" s="32"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="40" t="s">
+      <c r="H8" s="38"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="46" t="s">
         <v>106</v>
       </c>
-      <c r="K8" s="41"/>
-      <c r="L8" s="42"/>
+      <c r="K8" s="47"/>
+      <c r="L8" s="48"/>
     </row>
     <row r="9" spans="1:12" ht="33.75" customHeight="1">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="D6:L6"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:L4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="E1:H1"/>
+  <mergeCells count="25">
     <mergeCell ref="A9:L9"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
@@ -2627,6 +2617,19 @@
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="D6:L6"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:L4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2646,18 +2649,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2715,7 +2718,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="16" t="s">
         <v>80</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -2726,7 +2729,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="16" t="s">
         <v>81</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -2843,20 +2846,20 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="15" t="s">
         <v>108</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="16"/>
+      <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="61" t="s">
+      <c r="A22" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2923,11 +2926,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="61" t="s">
+      <c r="A31" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="54"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3021,16 +3024,16 @@
         <v>111</v>
       </c>
       <c r="B41" s="11"/>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="14" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="62" t="s">
+      <c r="A42" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="61"/>
-      <c r="C42" s="61"/>
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3131,28 +3134,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="56" t="s">
+      <c r="B52" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="57"/>
+      <c r="C52" s="50"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="57" t="s">
+      <c r="B53" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="57"/>
+      <c r="C53" s="50"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="57" t="s">
+      <c r="B54" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="57"/>
+      <c r="C54" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C283638-C8E3-412A-A4E4-B3752D34A34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F687D5-9224-48C9-B829-00E891B3CDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1338,7 +1338,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1490,6 +1490,12 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="新宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1865,12 +1871,66 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1907,59 +1967,8 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1982,23 +1991,20 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2417,198 +2423,218 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD1811D-72BB-4F54-B90A-4D27DF8394AD}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="6.625" customWidth="1"/>
-    <col min="3" max="3" width="6.5" customWidth="1"/>
-    <col min="4" max="5" width="6.625" customWidth="1"/>
-    <col min="6" max="6" width="6.5" customWidth="1"/>
-    <col min="7" max="8" width="6.625" customWidth="1"/>
-    <col min="9" max="9" width="6.5" customWidth="1"/>
-    <col min="10" max="10" width="9.625" customWidth="1"/>
-    <col min="11" max="11" width="8.625" customWidth="1"/>
-    <col min="12" max="12" width="4.625" customWidth="1"/>
+    <col min="1" max="1" width="6.625" customWidth="1"/>
+    <col min="2" max="3" width="7" customWidth="1"/>
+    <col min="4" max="4" width="6.625" customWidth="1"/>
+    <col min="5" max="6" width="7" customWidth="1"/>
+    <col min="7" max="7" width="6.625" customWidth="1"/>
+    <col min="8" max="9" width="7" customWidth="1"/>
+    <col min="10" max="10" width="6.625" customWidth="1"/>
+    <col min="11" max="12" width="5.625" customWidth="1"/>
+    <col min="13" max="13" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A1" s="20"/>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="56" t="s">
+    <row r="1" spans="1:13" ht="32.25" customHeight="1">
+      <c r="A1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-    </row>
-    <row r="2" spans="1:12" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A2" s="60" t="s">
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+    </row>
+    <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A2" s="57" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="61" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="58" t="s">
         <v>126</v>
       </c>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-    </row>
-    <row r="3" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A3" s="29" t="s">
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+    </row>
+    <row r="3" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A3" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="26" t="s">
+      <c r="B3" s="45"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="27"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="26" t="s">
+      <c r="E3" s="45"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="26" t="s">
+      <c r="H3" s="45"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="K3" s="27"/>
-      <c r="L3" s="30"/>
-    </row>
-    <row r="4" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A4" s="22" t="s">
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="48"/>
+    </row>
+    <row r="4" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A4" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="19"/>
-    </row>
-    <row r="5" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A5" s="32" t="s">
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="37"/>
+    </row>
+    <row r="5" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A5" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="17" t="s">
+      <c r="B5" s="18"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="35" t="s">
+      <c r="E5" s="21"/>
+      <c r="F5" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="36"/>
-    </row>
-    <row r="6" spans="1:12" ht="38.1" customHeight="1">
-      <c r="A6" s="32" t="s">
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="23"/>
+    </row>
+    <row r="6" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A6" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="17" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="19"/>
-    </row>
-    <row r="7" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A7" s="41" t="s">
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="37"/>
+    </row>
+    <row r="7" spans="1:13" ht="31.5" customHeight="1">
+      <c r="A7" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="44" t="s">
+      <c r="B7" s="29"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="44" t="s">
+      <c r="E7" s="31"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="44"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="57" t="s">
+      <c r="H7" s="31"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="K7" s="58"/>
-      <c r="L7" s="59"/>
-    </row>
-    <row r="8" spans="1:12" ht="31.5" customHeight="1" thickBot="1">
-      <c r="A8" s="40" t="s">
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="36"/>
+    </row>
+    <row r="8" spans="1:13" ht="48.75" customHeight="1" thickBot="1">
+      <c r="A8" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="37" t="s">
+      <c r="B8" s="25"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="37" t="s">
+      <c r="E8" s="25"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="H8" s="38"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="46" t="s">
+      <c r="H8" s="25"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="K8" s="47"/>
-      <c r="L8" s="48"/>
-    </row>
-    <row r="9" spans="1:12" ht="33.75" customHeight="1">
-      <c r="A9" s="31" t="s">
+      <c r="L8" s="33"/>
+      <c r="M8" s="61"/>
+    </row>
+    <row r="9" spans="1:13" ht="33.75" customHeight="1">
+      <c r="A9" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
+      <c r="K9" s="59"/>
+      <c r="L9" s="59"/>
+      <c r="M9" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:M4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A9:M9"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="F5:M5"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="G8:I8"/>
@@ -2616,23 +2642,12 @@
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="D6:L6"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:L4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="K8:L8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="11" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -2649,18 +2664,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2855,11 +2870,11 @@
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="54"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2926,11 +2941,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="54" t="s">
+      <c r="A31" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="54"/>
-      <c r="C31" s="54"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="55"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3029,11 +3044,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="55" t="s">
+      <c r="A42" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="54"/>
-      <c r="C42" s="54"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="55"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3134,28 +3149,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="49" t="s">
+      <c r="B52" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="50"/>
+      <c r="C52" s="51"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="50" t="s">
+      <c r="B53" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="50"/>
+      <c r="C53" s="51"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="50" t="s">
+      <c r="B54" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="50"/>
+      <c r="C54" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F687D5-9224-48C9-B829-00E891B3CDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB03209-FBD1-4655-A322-B941A47C91DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1517,7 +1517,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1813,13 +1813,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1871,6 +1889,78 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1884,9 +1974,6 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1919,57 +2006,18 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1991,20 +2039,14 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2029,13 +2071,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2083,13 +2125,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>428625</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2423,7 +2465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD1811D-72BB-4F54-B90A-4D27DF8394AD}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
@@ -2438,188 +2480,218 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A1" s="38"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="49" t="s">
+      <c r="A1" s="24"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="58" t="s">
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
     </row>
     <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="44" t="s">
+      <c r="B3" s="33"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="44" t="s">
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="H3" s="45"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="44" t="s">
+      <c r="H3" s="33"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="48"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="36"/>
     </row>
     <row r="4" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="43" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="37"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="31"/>
     </row>
     <row r="5" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="20" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="22" t="s">
+      <c r="E5" s="30"/>
+      <c r="F5" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="23"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="46"/>
     </row>
     <row r="6" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="20" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="37"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="31"/>
     </row>
     <row r="7" spans="1:13" ht="31.5" customHeight="1">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="31" t="s">
+      <c r="B7" s="52"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="31" t="s">
+      <c r="E7" s="54"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="34" t="s">
+      <c r="H7" s="54"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="36"/>
-    </row>
-    <row r="8" spans="1:13" ht="48.75" customHeight="1" thickBot="1">
-      <c r="A8" s="27" t="s">
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="58"/>
+    </row>
+    <row r="8" spans="1:13" ht="31.5" customHeight="1">
+      <c r="A8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="L8" s="69"/>
+      <c r="M8" s="68"/>
+    </row>
+    <row r="9" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A9" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="24" t="s">
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="24" t="s">
+      <c r="E9" s="48"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="H8" s="25"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="33" t="s">
-        <v>106</v>
-      </c>
-      <c r="L8" s="33"/>
-      <c r="M8" s="61"/>
-    </row>
-    <row r="9" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A9" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="59"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="22"/>
       <c r="K9" s="59"/>
       <c r="L9" s="59"/>
-      <c r="M9" s="59"/>
+      <c r="M9" s="23"/>
+    </row>
+    <row r="10" spans="1:13" ht="33.75" customHeight="1">
+      <c r="A10" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:M5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K8:L8"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="A4:C4"/>
@@ -2631,20 +2703,6 @@
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="I2:M2"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:M5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="K8:L8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2664,18 +2722,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2870,11 +2928,11 @@
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="55"/>
-      <c r="C22" s="55"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2941,11 +2999,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="55" t="s">
+      <c r="A31" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="55"/>
-      <c r="C31" s="55"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="65"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3044,11 +3102,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="56" t="s">
+      <c r="A42" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="55"/>
-      <c r="C42" s="55"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3149,28 +3207,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="50" t="s">
+      <c r="B52" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="51"/>
+      <c r="C52" s="61"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="51" t="s">
+      <c r="B53" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="51"/>
+      <c r="C53" s="61"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="51" t="s">
+      <c r="B54" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="51"/>
+      <c r="C54" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB03209-FBD1-4655-A322-B941A47C91DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9943422-E2AB-4AC7-A745-D7C8F1C8483F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1910,6 +1910,81 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1928,12 +2003,6 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1958,66 +2027,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2038,15 +2047,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2480,147 +2480,147 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="37" t="s">
+      <c r="A1" s="49"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="60" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="62" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="38" t="s">
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
     </row>
     <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="32" t="s">
+      <c r="B3" s="56"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="32" t="s">
+      <c r="E3" s="56"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="H3" s="33"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="32" t="s">
+      <c r="H3" s="56"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="55" t="s">
         <v>122</v>
       </c>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="36"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="59"/>
     </row>
     <row r="4" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29" t="s">
+      <c r="B4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="46"/>
     </row>
     <row r="5" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="44" t="s">
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="45" t="s">
+      <c r="E5" s="31"/>
+      <c r="F5" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="46"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="33"/>
     </row>
     <row r="6" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="44" t="s">
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="31"/>
-    </row>
-    <row r="7" spans="1:13" ht="31.5" customHeight="1">
-      <c r="A7" s="51" t="s">
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="46"/>
+    </row>
+    <row r="7" spans="1:13" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="54" t="s">
+      <c r="B7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="54"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="54" t="s">
+      <c r="E7" s="41"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="54"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="56" t="s">
+      <c r="H7" s="41"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="K7" s="57"/>
-      <c r="L7" s="57"/>
-      <c r="M7" s="58"/>
-    </row>
-    <row r="8" spans="1:13" ht="31.5" customHeight="1">
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="45"/>
+    </row>
+    <row r="8" spans="1:13" ht="29.1" customHeight="1">
       <c r="A8" s="17"/>
       <c r="B8" s="18"/>
       <c r="C8" s="19"/>
@@ -2630,53 +2630,64 @@
       <c r="G8" s="20"/>
       <c r="H8" s="20"/>
       <c r="I8" s="21"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="69" t="s">
+      <c r="J8" s="24"/>
+      <c r="K8" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="L8" s="69"/>
-      <c r="M8" s="68"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="25"/>
     </row>
     <row r="9" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="47" t="s">
+      <c r="B9" s="35"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="47" t="s">
+      <c r="E9" s="35"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="H9" s="48"/>
-      <c r="I9" s="49"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="36"/>
       <c r="J9" s="22"/>
-      <c r="K9" s="59"/>
-      <c r="L9" s="59"/>
+      <c r="K9" s="47"/>
+      <c r="L9" s="47"/>
       <c r="M9" s="23"/>
     </row>
     <row r="10" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:M4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
@@ -2692,17 +2703,6 @@
     <mergeCell ref="D6:M6"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K8:L8"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:M1"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:M4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2722,18 +2722,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2928,11 +2928,11 @@
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="65" t="s">
+      <c r="A22" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="65"/>
-      <c r="C22" s="65"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2999,11 +2999,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="65" t="s">
+      <c r="A31" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="65"/>
-      <c r="C31" s="65"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="68"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3102,11 +3102,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="66" t="s">
+      <c r="A42" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="68"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3207,28 +3207,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="60" t="s">
+      <c r="B52" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="61"/>
+      <c r="C52" s="64"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="61" t="s">
+      <c r="B53" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="61"/>
+      <c r="C53" s="64"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="61" t="s">
+      <c r="B54" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="61"/>
+      <c r="C54" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9943422-E2AB-4AC7-A745-D7C8F1C8483F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5815FD4C-861D-4786-9743-71869E92B2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1338,7 +1338,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1475,11 +1475,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="ˎ̥"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
@@ -1837,7 +1832,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1892,75 +1887,81 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -1976,57 +1977,9 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2047,6 +2000,39 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2480,214 +2466,203 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A1" s="49"/>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="60" t="s">
+      <c r="A1" s="22"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="61" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
     </row>
     <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="55" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="56"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="55" t="s">
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="H3" s="56"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="55" t="s">
+      <c r="H3" s="31"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="59"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="34"/>
     </row>
     <row r="4" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="54" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="46"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="29"/>
     </row>
     <row r="5" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="30" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="32" t="s">
+      <c r="E5" s="28"/>
+      <c r="F5" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="33"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="41"/>
     </row>
     <row r="6" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="30" t="s">
+      <c r="B6" s="25"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="46"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="29"/>
     </row>
     <row r="7" spans="1:13" ht="33.950000000000003" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="42" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="41" t="s">
+      <c r="B7" s="56"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="41" t="s">
+      <c r="E7" s="43"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="41"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="43" t="s">
+      <c r="H7" s="43"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="45"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="47"/>
     </row>
     <row r="8" spans="1:13" ht="29.1" customHeight="1">
       <c r="A8" s="17"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="24"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="20"/>
       <c r="K8" s="48" t="s">
         <v>106</v>
       </c>
       <c r="L8" s="48"/>
-      <c r="M8" s="25"/>
+      <c r="M8" s="21"/>
     </row>
     <row r="9" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="60" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="34" t="s">
+      <c r="B9" s="61"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="63" t="s">
         <v>113</v>
       </c>
-      <c r="E9" s="35"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="34" t="s">
+      <c r="E9" s="61"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="63" t="s">
         <v>113</v>
       </c>
-      <c r="H9" s="35"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="23"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="65"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="66"/>
     </row>
     <row r="10" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:M1"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:M4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
@@ -2703,6 +2678,17 @@
     <mergeCell ref="D6:M6"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K8:L8"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:M4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2722,18 +2708,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2928,11 +2914,11 @@
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="68" t="s">
+      <c r="A22" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2999,11 +2985,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="68" t="s">
+      <c r="A31" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="54"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3102,11 +3088,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="69" t="s">
+      <c r="A42" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68"/>
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3207,28 +3193,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="63" t="s">
+      <c r="B52" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="64"/>
+      <c r="C52" s="50"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="64" t="s">
+      <c r="B53" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="64"/>
+      <c r="C53" s="50"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="64" t="s">
+      <c r="B54" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="64"/>
+      <c r="C54" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5815FD4C-861D-4786-9743-71869E92B2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB75D38-6781-415A-A535-01A6233FE003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="128">
   <si>
     <t>请假期间</t>
   </si>
@@ -1332,13 +1332,17 @@
   </si>
   <si>
     <t>单号：{{单据号}}</t>
+  </si>
+  <si>
+    <t>小红</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1491,6 +1495,13 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1899,30 +1910,93 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1947,39 +2021,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2001,38 +2042,8 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2466,150 +2477,150 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A1" s="22"/>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="35" t="s">
+      <c r="A1" s="48"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="58" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="36" t="s">
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="57" t="s">
         <v>126</v>
       </c>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
     </row>
     <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="30" t="s">
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="30" t="s">
+      <c r="E3" s="52"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="30" t="s">
+      <c r="H3" s="52"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="51" t="s">
         <v>122</v>
       </c>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="34"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="55"/>
     </row>
     <row r="4" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="27" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="29"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="45"/>
     </row>
     <row r="5" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="39" t="s">
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="40" t="s">
+      <c r="E5" s="30"/>
+      <c r="F5" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="41"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="32"/>
     </row>
     <row r="6" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="39" t="s">
+      <c r="B6" s="27"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="29"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="45"/>
     </row>
     <row r="7" spans="1:13" ht="33.950000000000003" customHeight="1">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="56"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="43" t="s">
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="43"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="43" t="s">
+      <c r="E7" s="40"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="43"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="45" t="s">
+      <c r="H7" s="40"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="47"/>
+      <c r="K7" s="43"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="44"/>
     </row>
     <row r="8" spans="1:13" ht="29.1" customHeight="1">
       <c r="A8" s="17"/>
-      <c r="B8" s="58"/>
-      <c r="C8" s="59"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="23"/>
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
       <c r="F8" s="19"/>
@@ -2617,52 +2628,65 @@
       <c r="H8" s="18"/>
       <c r="I8" s="19"/>
       <c r="J8" s="20"/>
-      <c r="K8" s="48" t="s">
+      <c r="K8" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="L8" s="48"/>
+      <c r="L8" s="47"/>
       <c r="M8" s="21"/>
     </row>
     <row r="9" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="63" t="s">
+      <c r="B9" s="34"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="E9" s="61"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="63" t="s">
+      <c r="E9" s="34"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="H9" s="61"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="64"/>
-      <c r="K9" s="65"/>
-      <c r="L9" s="65"/>
-      <c r="M9" s="66"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="66" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="10" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:M4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
@@ -2678,17 +2702,6 @@
     <mergeCell ref="D6:M6"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K8:L8"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:M1"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:M4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2708,18 +2721,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2914,11 +2927,11 @@
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="54"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="64"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2985,11 +2998,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="54" t="s">
+      <c r="A31" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="54"/>
-      <c r="C31" s="54"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="64"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3088,11 +3101,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="55" t="s">
+      <c r="A42" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="54"/>
-      <c r="C42" s="54"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3193,28 +3206,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="49" t="s">
+      <c r="B52" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="50"/>
+      <c r="C52" s="60"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="50" t="s">
+      <c r="B53" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="50"/>
+      <c r="C53" s="60"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="50" t="s">
+      <c r="B54" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="50"/>
+      <c r="C54" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB75D38-6781-415A-A535-01A6233FE003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796FBF41-3366-4D49-ADEC-88A90E1E776B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1497,7 +1497,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -1919,25 +1919,61 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1979,47 +2015,11 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2477,145 +2477,145 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A1" s="48"/>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="56" t="s">
+      <c r="A1" s="25"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="57" t="s">
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
     </row>
     <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="51" t="s">
+      <c r="B3" s="34"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="52"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="51" t="s">
+      <c r="E3" s="34"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="H3" s="52"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="51" t="s">
+      <c r="H3" s="34"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="55"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="37"/>
     </row>
     <row r="4" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="50" t="s">
+      <c r="B4" s="28"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="45"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="32"/>
     </row>
     <row r="5" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29" t="s">
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="31" t="s">
+      <c r="E5" s="31"/>
+      <c r="F5" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="32"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="44"/>
     </row>
     <row r="6" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29" t="s">
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="42" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="45"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="32"/>
     </row>
     <row r="7" spans="1:13" ht="33.950000000000003" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="40" t="s">
+      <c r="B7" s="50"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="40"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="40" t="s">
+      <c r="E7" s="52"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="40"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="42" t="s">
+      <c r="H7" s="52"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="44"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="56"/>
     </row>
     <row r="8" spans="1:13" ht="29.1" customHeight="1">
       <c r="A8" s="17"/>
@@ -2628,65 +2628,54 @@
       <c r="H8" s="18"/>
       <c r="I8" s="19"/>
       <c r="J8" s="20"/>
-      <c r="K8" s="47" t="s">
+      <c r="K8" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="L8" s="47"/>
+      <c r="L8" s="58"/>
       <c r="M8" s="21"/>
     </row>
     <row r="9" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="33" t="s">
+      <c r="B9" s="46"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="E9" s="34"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="33" t="s">
+      <c r="E9" s="46"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="H9" s="34"/>
-      <c r="I9" s="35"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="47"/>
       <c r="J9" s="24"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
       <c r="M9" s="66" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:M1"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:M4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
@@ -2702,6 +2691,17 @@
     <mergeCell ref="D6:M6"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K8:L8"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:M4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796FBF41-3366-4D49-ADEC-88A90E1E776B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A5DAC7-1FB7-488C-85BC-8B00CC9F8550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="9240" windowHeight="18660" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="127">
   <si>
     <t>请假期间</t>
   </si>
@@ -1332,10 +1332,6 @@
   </si>
   <si>
     <t>单号：{{单据号}}</t>
-  </si>
-  <si>
-    <t>小红</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1919,30 +1915,87 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1967,60 +2020,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2041,9 +2040,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2477,63 +2473,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A1" s="25"/>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="38" t="s">
+      <c r="A1" s="49"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="39" t="s">
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="58" t="s">
         <v>126</v>
       </c>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
     </row>
     <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="33" t="s">
+      <c r="B3" s="53"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="52" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="33" t="s">
+      <c r="E3" s="53"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="33" t="s">
+      <c r="H3" s="53"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="37"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="56"/>
     </row>
     <row r="4" spans="1:13" ht="45.95" customHeight="1">
       <c r="A4" s="27" t="s">
@@ -2541,7 +2537,7 @@
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="29"/>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="51" t="s">
         <v>104</v>
       </c>
       <c r="E4" s="31"/>
@@ -2552,7 +2548,7 @@
       <c r="J4" s="31"/>
       <c r="K4" s="31"/>
       <c r="L4" s="31"/>
-      <c r="M4" s="32"/>
+      <c r="M4" s="46"/>
     </row>
     <row r="5" spans="1:13" ht="45.95" customHeight="1">
       <c r="A5" s="27" t="s">
@@ -2560,20 +2556,20 @@
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="29"/>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="30" t="s">
         <v>123</v>
       </c>
       <c r="E5" s="31"/>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="44"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="33"/>
     </row>
     <row r="6" spans="1:13" ht="45.95" customHeight="1">
       <c r="A6" s="27" t="s">
@@ -2581,7 +2577,7 @@
       </c>
       <c r="B6" s="28"/>
       <c r="C6" s="29"/>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="30" t="s">
         <v>124</v>
       </c>
       <c r="E6" s="31"/>
@@ -2592,30 +2588,30 @@
       <c r="J6" s="31"/>
       <c r="K6" s="31"/>
       <c r="L6" s="31"/>
-      <c r="M6" s="32"/>
-    </row>
-    <row r="7" spans="1:13" ht="33.950000000000003" customHeight="1">
-      <c r="A7" s="49" t="s">
+      <c r="M6" s="46"/>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A7" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="52" t="s">
+      <c r="B7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="52"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="52" t="s">
+      <c r="E7" s="41"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="52"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="54" t="s">
+      <c r="H7" s="41"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="56"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="45"/>
     </row>
     <row r="8" spans="1:13" ht="29.1" customHeight="1">
       <c r="A8" s="17"/>
@@ -2628,54 +2624,63 @@
       <c r="H8" s="18"/>
       <c r="I8" s="19"/>
       <c r="J8" s="20"/>
-      <c r="K8" s="58" t="s">
+      <c r="K8" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="L8" s="58"/>
+      <c r="L8" s="48"/>
       <c r="M8" s="21"/>
     </row>
-    <row r="9" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A9" s="48" t="s">
+    <row r="9" spans="1:13" ht="10.5" customHeight="1" thickBot="1">
+      <c r="A9" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="45" t="s">
+      <c r="B9" s="35"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="E9" s="46"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="45" t="s">
+      <c r="E9" s="35"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="H9" s="46"/>
-      <c r="I9" s="47"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="36"/>
       <c r="J9" s="24"/>
-      <c r="K9" s="57"/>
-      <c r="L9" s="57"/>
-      <c r="M9" s="66" t="s">
-        <v>127</v>
-      </c>
+      <c r="K9" s="47"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="25"/>
     </row>
     <row r="10" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:M4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:M10"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
@@ -2691,17 +2696,6 @@
     <mergeCell ref="D6:M6"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K8:L8"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:M1"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:M4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2721,18 +2715,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2927,11 +2921,11 @@
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="64" t="s">
+      <c r="A22" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="64"/>
-      <c r="C22" s="64"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2998,11 +2992,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="64" t="s">
+      <c r="A31" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="64"/>
-      <c r="C31" s="64"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="65"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3101,11 +3095,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="65" t="s">
+      <c r="A42" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="64"/>
-      <c r="C42" s="64"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3206,28 +3200,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="59" t="s">
+      <c r="B52" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="60"/>
+      <c r="C52" s="61"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="60" t="s">
+      <c r="B53" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="60"/>
+      <c r="C53" s="61"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="60" t="s">
+      <c r="B54" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="60"/>
+      <c r="C54" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A5DAC7-1FB7-488C-85BC-8B00CC9F8550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A74946-BA39-49B8-BC31-1A7990B0FCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="9240" windowHeight="18660" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="3" r:id="rId1"/>
@@ -1042,9 +1042,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>如果“请假类别”为“其它”，请在“请假事由”中备注情况</t>
-  </si>
-  <si>
     <t>{{说明}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1332,13 +1329,17 @@
   </si>
   <si>
     <t>单号：{{单据号}}</t>
+  </si>
+  <si>
+    <t>如“请假类别”为“其它”，请在“请假事由”中备注情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1443,18 +1444,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="新宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -1839,7 +1828,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1891,134 +1880,65 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2040,6 +1960,64 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2473,145 +2451,145 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A1" s="49"/>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="57" t="s">
-        <v>105</v>
-      </c>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
+      <c r="A1" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="49" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="58" t="s">
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+    </row>
+    <row r="3" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A3" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="44"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" s="44"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="44"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="50"/>
+    </row>
+    <row r="4" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A4" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="51"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="47"/>
+    </row>
+    <row r="5" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A5" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="31"/>
+      <c r="F5" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-    </row>
-    <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="52" t="s">
-        <v>120</v>
-      </c>
-      <c r="E3" s="53"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="H3" s="53"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="56"/>
-    </row>
-    <row r="4" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A4" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="46"/>
-    </row>
-    <row r="5" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A5" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="30" t="s">
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="65"/>
+    </row>
+    <row r="6" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A6" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="51"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="33"/>
-    </row>
-    <row r="6" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A6" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="47"/>
     </row>
     <row r="7" spans="1:13" ht="36.75" customHeight="1">
-      <c r="A7" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="41" t="s">
+      <c r="A7" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="54"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="41" t="s">
+      <c r="H7" s="54"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="41"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="45"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="62"/>
     </row>
     <row r="8" spans="1:13" ht="29.1" customHeight="1">
       <c r="A8" s="17"/>
@@ -2624,78 +2602,58 @@
       <c r="H8" s="18"/>
       <c r="I8" s="19"/>
       <c r="J8" s="20"/>
-      <c r="K8" s="48" t="s">
-        <v>106</v>
-      </c>
-      <c r="L8" s="48"/>
+      <c r="K8" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="L8" s="36"/>
       <c r="M8" s="21"/>
     </row>
     <row r="9" spans="1:13" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="58"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="60" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" s="35"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="H9" s="35"/>
-      <c r="I9" s="36"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="60" t="s">
+        <v>112</v>
+      </c>
+      <c r="H9" s="58"/>
+      <c r="I9" s="59"/>
       <c r="J9" s="24"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="47"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="25"/>
     </row>
     <row r="10" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="63"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:M1"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:M4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A5:C5"/>
+  <mergeCells count="6">
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:M5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="D6:M6"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K8:L8"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2715,18 +2673,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2788,7 +2746,7 @@
         <v>80</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>82</v>
@@ -2799,7 +2757,7 @@
         <v>81</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>82</v>
@@ -2913,19 +2871,19 @@
     </row>
     <row r="21" spans="1:3" ht="17.25" thickBot="1">
       <c r="A21" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="65" t="s">
+      <c r="A22" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="65"/>
-      <c r="C22" s="65"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2992,11 +2950,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="65" t="s">
+      <c r="A31" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="65"/>
-      <c r="C31" s="65"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="42"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3087,19 +3045,19 @@
     </row>
     <row r="41" spans="1:3" ht="17.25" thickBot="1">
       <c r="A41" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B41" s="11"/>
       <c r="C41" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="66" t="s">
+      <c r="A42" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="42"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3200,28 +3158,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="60" t="s">
+      <c r="B52" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="61"/>
+      <c r="C52" s="38"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="61" t="s">
+      <c r="B53" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="61"/>
+      <c r="C53" s="38"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="61" t="s">
+      <c r="B54" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="61"/>
+      <c r="C54" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A74946-BA39-49B8-BC31-1A7990B0FCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F871D5EE-025D-4B80-9CB4-38542A4A3502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1508,7 +1508,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1741,59 +1741,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1822,13 +1769,98 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1889,10 +1921,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1907,32 +1939,32 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1961,63 +1993,74 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2451,145 +2494,145 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="33" t="s">
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
     </row>
     <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="29" t="s">
+      <c r="B3" s="53"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="29" t="s">
+      <c r="E3" s="61"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="60" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="44"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="29" t="s">
+      <c r="H3" s="61"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="50"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="63"/>
     </row>
     <row r="4" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="28" t="s">
+      <c r="B4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="47"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="65"/>
     </row>
     <row r="5" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="34" t="s">
+      <c r="B5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="64" t="s">
+      <c r="E5" s="27"/>
+      <c r="F5" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="65"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="51"/>
     </row>
     <row r="6" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="26" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="47"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="28"/>
     </row>
     <row r="7" spans="1:13" ht="36.75" customHeight="1">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="18" t="s">
+      <c r="B7" s="33"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="E7" s="54"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="18" t="s">
+      <c r="E7" s="33"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="H7" s="54"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="27" t="s">
+      <c r="H7" s="33"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="K7" s="61"/>
-      <c r="L7" s="61"/>
-      <c r="M7" s="62"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="34"/>
     </row>
     <row r="8" spans="1:13" ht="29.1" customHeight="1">
       <c r="A8" s="17"/>
@@ -2609,51 +2652,65 @@
       <c r="M8" s="21"/>
     </row>
     <row r="9" spans="1:13" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="60" t="s">
+      <c r="B9" s="46"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="60" t="s">
+      <c r="E9" s="46"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="H9" s="58"/>
-      <c r="I9" s="59"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="47"/>
       <c r="J9" s="24"/>
       <c r="K9" s="35"/>
       <c r="L9" s="35"/>
       <c r="M9" s="25"/>
     </row>
     <row r="10" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A10" s="63" t="s">
+      <c r="A10" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="63"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="63"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="63"/>
-      <c r="M10" s="63"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="20">
+    <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:M5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="D6:M6"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K8:L8"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:M4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:M3"/>
     <mergeCell ref="I2:M2"/>
     <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F871D5EE-025D-4B80-9CB4-38542A4A3502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD10D589-BC39-4CBC-9539-3C5FE58E79AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1339,7 +1339,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1487,6 +1487,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1915,24 +1922,12 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2061,6 +2056,18 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2494,200 +2501,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="62" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="30" t="s">
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
     </row>
     <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="60" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="61"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="60" t="s">
+      <c r="E3" s="57"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="60" t="s">
+      <c r="H3" s="57"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="K3" s="61"/>
-      <c r="L3" s="61"/>
-      <c r="M3" s="63"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="59"/>
     </row>
     <row r="4" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="26" t="s">
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="65"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="61"/>
     </row>
     <row r="5" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="31" t="s">
+      <c r="B5" s="54"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="50" t="s">
+      <c r="E5" s="23"/>
+      <c r="F5" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="51"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="47"/>
     </row>
     <row r="6" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="31" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="28"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="24"/>
     </row>
     <row r="7" spans="1:13" ht="36.75" customHeight="1">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="32" t="s">
+      <c r="B7" s="29"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="E7" s="33"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="32" t="s">
+      <c r="E7" s="29"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="H7" s="33"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="32" t="s">
+      <c r="H7" s="29"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="34"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="30"/>
     </row>
     <row r="8" spans="1:13" ht="29.1" customHeight="1">
       <c r="A8" s="17"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="36" t="s">
+      <c r="B8" s="19"/>
+      <c r="C8" s="63">
+        <v>1</v>
+      </c>
+      <c r="D8" s="64">
+        <v>1</v>
+      </c>
+      <c r="E8" s="64">
+        <v>1</v>
+      </c>
+      <c r="F8" s="65">
+        <v>1</v>
+      </c>
+      <c r="G8" s="64">
+        <v>1</v>
+      </c>
+      <c r="H8" s="64">
+        <v>1</v>
+      </c>
+      <c r="I8" s="65">
+        <v>1</v>
+      </c>
+      <c r="J8" s="66">
+        <v>1</v>
+      </c>
+      <c r="K8" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="L8" s="36"/>
-      <c r="M8" s="21"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="18"/>
     </row>
     <row r="9" spans="1:13" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="48" t="s">
+      <c r="B9" s="42"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="E9" s="46"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="48" t="s">
+      <c r="E9" s="42"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="H9" s="46"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="25"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="21"/>
     </row>
     <row r="10" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="45"/>
+      <c r="M10" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -2730,18 +2753,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2936,11 +2959,11 @@
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="42"/>
-      <c r="C22" s="42"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -3007,11 +3030,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="42"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3110,11 +3133,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="43" t="s">
+      <c r="A42" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="42"/>
-      <c r="C42" s="42"/>
+      <c r="B42" s="38"/>
+      <c r="C42" s="38"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3215,28 +3238,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="37" t="s">
+      <c r="B52" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="38"/>
+      <c r="C52" s="34"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="38" t="s">
+      <c r="B53" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="38"/>
+      <c r="C53" s="34"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="38" t="s">
+      <c r="B54" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="38"/>
+      <c r="C54" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD10D589-BC39-4CBC-9539-3C5FE58E79AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D004246-8B95-464D-8E9E-37CBBF8D3749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="125">
   <si>
     <t>请假期间</t>
   </si>
@@ -1104,16 +1104,6 @@
       </rPr>
       <t>}}</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-　               </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1339,7 +1329,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1481,13 +1471,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="6"/>
-      <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="0"/>
       <name val="微软雅黑"/>
@@ -1515,7 +1498,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1730,24 +1713,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1755,24 +1720,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1867,7 +1814,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1919,21 +1866,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1952,7 +1884,7 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1961,12 +1893,6 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1991,18 +1917,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2012,19 +1926,19 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2036,16 +1950,16 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2057,16 +1971,28 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
@@ -2093,12 +2019,12 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2118,60 +2044,6 @@
         <a:xfrm>
           <a:off x="1819275" y="2800350"/>
           <a:ext cx="0" cy="981075"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>428625</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Line 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5FB8E98-3F47-4A77-AEA7-8DB83B5C8ED7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3638550" y="2781300"/>
-          <a:ext cx="0" cy="419100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2486,7 +2358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD1811D-72BB-4F54-B90A-4D27DF8394AD}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
@@ -2501,219 +2373,198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+    </row>
+    <row r="3" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A3" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="E3" s="46"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="46"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="48"/>
+    </row>
+    <row r="4" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A4" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="50"/>
+    </row>
+    <row r="5" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A5" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="43"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="F5" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-    </row>
-    <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="48" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="E3" s="57"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="H3" s="57"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="56" t="s">
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="36"/>
+    </row>
+    <row r="6" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A6" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="43"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="59"/>
-    </row>
-    <row r="4" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A4" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="61"/>
-    </row>
-    <row r="5" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A5" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="47"/>
-    </row>
-    <row r="6" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A6" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="24"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="19"/>
     </row>
     <row r="7" spans="1:13" ht="36.75" customHeight="1">
-      <c r="A7" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="28" t="s">
+      <c r="A7" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="24"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="24"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="H7" s="24"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="H7" s="29"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="30"/>
-    </row>
-    <row r="8" spans="1:13" ht="29.1" customHeight="1">
-      <c r="A8" s="17"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="63">
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="25"/>
+    </row>
+    <row r="8" spans="1:13" ht="29.1" customHeight="1" thickBot="1">
+      <c r="A8" s="52"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="54">
         <v>1</v>
       </c>
-      <c r="D8" s="64">
+      <c r="D8" s="55">
         <v>1</v>
       </c>
-      <c r="E8" s="64">
+      <c r="E8" s="55">
         <v>1</v>
       </c>
-      <c r="F8" s="65">
+      <c r="F8" s="56">
         <v>1</v>
       </c>
-      <c r="G8" s="64">
+      <c r="G8" s="55">
         <v>1</v>
       </c>
-      <c r="H8" s="64">
+      <c r="H8" s="55">
         <v>1</v>
       </c>
-      <c r="I8" s="65">
+      <c r="I8" s="56">
         <v>1</v>
       </c>
-      <c r="J8" s="66">
+      <c r="J8" s="57">
         <v>1</v>
       </c>
-      <c r="K8" s="32" t="s">
+      <c r="K8" s="58" t="s">
         <v>105</v>
       </c>
-      <c r="L8" s="32"/>
-      <c r="M8" s="18"/>
-    </row>
-    <row r="9" spans="1:13" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A9" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" s="42"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="H9" s="42"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="21"/>
-    </row>
-    <row r="10" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A10" s="45" t="s">
+      <c r="L8" s="58"/>
+      <c r="M8" s="59"/>
+    </row>
+    <row r="9" spans="1:13" ht="33.75" customHeight="1">
+      <c r="A9" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="19">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:M5"/>
@@ -2723,7 +2574,6 @@
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="J7:M7"/>
     <mergeCell ref="D6:M6"/>
-    <mergeCell ref="K9:L9"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:M4"/>
@@ -2753,18 +2603,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2959,11 +2809,11 @@
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="38"/>
-      <c r="C22" s="38"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -3030,11 +2880,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="38"/>
-      <c r="C31" s="38"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3129,15 +2979,15 @@
       </c>
       <c r="B41" s="11"/>
       <c r="C41" s="14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="39" t="s">
+      <c r="A42" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="38"/>
-      <c r="C42" s="38"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="31"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3238,28 +3088,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="33" t="s">
+      <c r="B52" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="34"/>
+      <c r="C52" s="27"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="34" t="s">
+      <c r="B53" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="34"/>
+      <c r="C53" s="27"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="34" t="s">
+      <c r="B54" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="34"/>
+      <c r="C54" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D004246-8B95-464D-8E9E-37CBBF8D3749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E5E0A7-4071-4151-ADCF-9DEB47EB2E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1498,7 +1498,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1713,6 +1713,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1720,6 +1738,24 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1803,6 +1839,15 @@
         <color indexed="64"/>
       </right>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -1814,7 +1859,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1872,9 +1917,6 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1884,15 +1926,6 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1917,8 +1950,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1926,20 +1965,14 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1950,16 +1983,16 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1971,20 +2004,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -1994,6 +2021,57 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2018,13 +2096,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2358,7 +2436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD1811D-72BB-4F54-B90A-4D27DF8394AD}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
@@ -2373,208 +2451,210 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="21" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="45" t="s">
+      <c r="B3" s="36"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="E3" s="46"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="45" t="s">
+      <c r="E3" s="42"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="46"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="45" t="s">
+      <c r="H3" s="42"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="48"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="44"/>
     </row>
     <row r="4" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="44"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="40"/>
       <c r="D4" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="50"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="46"/>
     </row>
     <row r="5" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="22" t="s">
+      <c r="B5" s="39"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="21" t="s">
         <v>120</v>
       </c>
       <c r="E5" s="18"/>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="36"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="34"/>
     </row>
     <row r="6" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="22" t="s">
+      <c r="B6" s="49"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="62" t="s">
         <v>121</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="19"/>
-    </row>
-    <row r="7" spans="1:13" ht="36.75" customHeight="1">
-      <c r="A7" s="40" t="s">
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="64"/>
+    </row>
+    <row r="7" spans="1:13" ht="12" customHeight="1">
+      <c r="A7" s="56"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="60"/>
+      <c r="L7" s="60"/>
+      <c r="M7" s="61"/>
+    </row>
+    <row r="8" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A8" s="65" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="23" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="E7" s="24"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="23" t="s">
+      <c r="E8" s="66"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="68" t="s">
         <v>112</v>
       </c>
-      <c r="H7" s="24"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="23" t="s">
+      <c r="H8" s="66"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="68" t="s">
         <v>113</v>
       </c>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="25"/>
-    </row>
-    <row r="8" spans="1:13" ht="29.1" customHeight="1" thickBot="1">
-      <c r="A8" s="52"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="54">
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="69"/>
+    </row>
+    <row r="9" spans="1:13" ht="29.1" customHeight="1" thickBot="1">
+      <c r="A9" s="55"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="51">
         <v>1</v>
       </c>
-      <c r="D8" s="55">
+      <c r="K9" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="L9" s="52"/>
+      <c r="M9" s="53"/>
+    </row>
+    <row r="10" spans="1:13" ht="33.75" customHeight="1">
+      <c r="A10" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="55">
-        <v>1</v>
-      </c>
-      <c r="F8" s="56">
-        <v>1</v>
-      </c>
-      <c r="G8" s="55">
-        <v>1</v>
-      </c>
-      <c r="H8" s="55">
-        <v>1</v>
-      </c>
-      <c r="I8" s="56">
-        <v>1</v>
-      </c>
-      <c r="J8" s="57">
-        <v>1</v>
-      </c>
-      <c r="K8" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="L8" s="58"/>
-      <c r="M8" s="59"/>
-    </row>
-    <row r="9" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A9" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
+    <mergeCell ref="A8:C9"/>
+    <mergeCell ref="D8:F9"/>
+    <mergeCell ref="G8:I9"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:M5"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="J8:M8"/>
     <mergeCell ref="D6:M6"/>
-    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="A10:M10"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:M4"/>
     <mergeCell ref="D3:F3"/>
@@ -2603,18 +2683,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2809,11 +2889,11 @@
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2880,11 +2960,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -2983,11 +3063,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="32" t="s">
+      <c r="A42" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3088,28 +3168,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="26" t="s">
+      <c r="B52" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="27"/>
+      <c r="C52" s="23"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="27"/>
+      <c r="C53" s="23"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="27"/>
+      <c r="C54" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E5E0A7-4071-4151-ADCF-9DEB47EB2E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5708FE-B6D8-40BB-897B-3CF94E186F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1498,7 +1498,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1844,22 +1844,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1965,15 +1956,6 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2022,9 +2004,6 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
@@ -2071,6 +2050,24 @@
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -2096,13 +2093,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2436,7 +2433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD1811D-72BB-4F54-B90A-4D27DF8394AD}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
@@ -2468,14 +2465,14 @@
       <c r="M1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
       <c r="G2" s="29"/>
       <c r="H2" s="29"/>
       <c r="I2" s="20" t="s">
@@ -2487,53 +2484,53 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="72" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="41" t="s">
+      <c r="B3" s="39"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="E3" s="42"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="41" t="s">
+      <c r="E3" s="39"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="42"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="41" t="s">
+      <c r="H3" s="39"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="44"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="41"/>
     </row>
     <row r="4" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="40"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="37"/>
       <c r="D4" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="46"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="43"/>
     </row>
     <row r="5" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="40"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
       <c r="D5" s="21" t="s">
         <v>120</v>
       </c>
@@ -2550,64 +2547,64 @@
       <c r="M5" s="34"/>
     </row>
     <row r="6" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="62" t="s">
+      <c r="B6" s="46"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="63"/>
-      <c r="L6" s="63"/>
-      <c r="M6" s="64"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="60"/>
     </row>
     <row r="7" spans="1:13" ht="12" customHeight="1">
-      <c r="A7" s="56"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="61"/>
-    </row>
-    <row r="8" spans="1:13" ht="36.75" customHeight="1">
-      <c r="A8" s="65" t="s">
+      <c r="A7" s="52"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
+    </row>
+    <row r="8" spans="1:13" ht="32.25" customHeight="1">
+      <c r="A8" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="66"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="68" t="s">
+      <c r="B8" s="62"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="64" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="66"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="68" t="s">
+      <c r="E8" s="62"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="H8" s="66"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="68" t="s">
+      <c r="H8" s="62"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="K8" s="66"/>
-      <c r="L8" s="66"/>
-      <c r="M8" s="69"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="65"/>
     </row>
     <row r="9" spans="1:13" ht="29.1" customHeight="1" thickBot="1">
-      <c r="A9" s="55"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="31"/>
       <c r="C9" s="32"/>
       <c r="D9" s="30"/>
@@ -2616,31 +2613,46 @@
       <c r="G9" s="30"/>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
-      <c r="J9" s="51">
+      <c r="J9" s="48">
         <v>1</v>
       </c>
-      <c r="K9" s="52" t="s">
+      <c r="K9" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="L9" s="52"/>
-      <c r="M9" s="53"/>
-    </row>
-    <row r="10" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A10" s="54" t="s">
+      <c r="L9" s="49"/>
+      <c r="M9" s="50"/>
+    </row>
+    <row r="10" spans="1:13" ht="6.75" customHeight="1">
+      <c r="A10" s="67"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="68"/>
+      <c r="K10" s="69"/>
+      <c r="L10" s="69"/>
+      <c r="M10" s="70"/>
+    </row>
+    <row r="11" spans="1:13" ht="33.75" customHeight="1">
+      <c r="A11" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -2654,7 +2666,7 @@
     <mergeCell ref="J8:M8"/>
     <mergeCell ref="D6:M6"/>
     <mergeCell ref="K9:L9"/>
-    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A11:M11"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:M4"/>
     <mergeCell ref="D3:F3"/>

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5708FE-B6D8-40BB-897B-3CF94E186F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406D5D9F-8614-476E-9007-049B19E00D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1498,7 +1498,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1844,6 +1844,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2052,23 +2061,23 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2484,7 +2493,7 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="68" t="s">
         <v>116</v>
       </c>
       <c r="B3" s="39"/>
@@ -2613,9 +2622,7 @@
       <c r="G9" s="30"/>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
-      <c r="J9" s="48">
-        <v>1</v>
-      </c>
+      <c r="J9" s="48"/>
       <c r="K9" s="49" t="s">
         <v>105</v>
       </c>
@@ -2623,36 +2630,36 @@
       <c r="M9" s="50"/>
     </row>
     <row r="10" spans="1:13" ht="6.75" customHeight="1">
-      <c r="A10" s="67"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
-      <c r="J10" s="68"/>
-      <c r="K10" s="69"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="70"/>
-    </row>
-    <row r="11" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A11" s="71" t="s">
+      <c r="A10" s="69"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="72"/>
+    </row>
+    <row r="11" spans="1:13" ht="27.75" customHeight="1">
+      <c r="A11" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="71"/>
-      <c r="M11" s="71"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406D5D9F-8614-476E-9007-049B19E00D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F49F096-CA91-49F2-92C0-9DADC2F26E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -2061,9 +2061,6 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2078,6 +2075,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2493,7 +2493,7 @@
       <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="67" t="s">
         <v>116</v>
       </c>
       <c r="B3" s="39"/>
@@ -2574,7 +2574,7 @@
       <c r="L6" s="59"/>
       <c r="M6" s="60"/>
     </row>
-    <row r="7" spans="1:13" ht="12" customHeight="1">
+    <row r="7" spans="1:13" ht="13.5" customHeight="1">
       <c r="A7" s="52"/>
       <c r="B7" s="53"/>
       <c r="C7" s="54"/>
@@ -2630,36 +2630,36 @@
       <c r="M9" s="50"/>
     </row>
     <row r="10" spans="1:13" ht="6.75" customHeight="1">
-      <c r="A10" s="69"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="70"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="71"/>
-      <c r="M10" s="72"/>
+      <c r="A10" s="68"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="69"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="70"/>
+      <c r="M10" s="71"/>
     </row>
     <row r="11" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A11" s="67" t="s">
+      <c r="A11" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
-      <c r="J11" s="67"/>
-      <c r="K11" s="67"/>
-      <c r="L11" s="67"/>
-      <c r="M11" s="67"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="72"/>
+      <c r="M11" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F49F096-CA91-49F2-92C0-9DADC2F26E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D9A285-1246-4E41-B96B-BDA7850D5C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1911,20 +1911,152 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1946,138 +2078,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2457,212 +2457,222 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="64" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="65" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="20" t="s">
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
     </row>
     <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="38" t="s">
+      <c r="B3" s="59"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="38" t="s">
+      <c r="E3" s="59"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="39"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="38" t="s">
+      <c r="H3" s="59"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="41"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="62"/>
     </row>
     <row r="4" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="17" t="s">
+      <c r="B4" s="40"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="43"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="57"/>
     </row>
     <row r="5" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="21" t="s">
+      <c r="B5" s="40"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="33" t="s">
+      <c r="E5" s="43"/>
+      <c r="F5" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="34"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="45"/>
     </row>
     <row r="6" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="58" t="s">
+      <c r="B6" s="47"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="60"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="52"/>
     </row>
     <row r="7" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A7" s="52"/>
-      <c r="B7" s="53"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
-    </row>
-    <row r="8" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A8" s="61" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="25"/>
+    </row>
+    <row r="8" spans="1:13" ht="26.1" customHeight="1">
+      <c r="A8" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="62"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="64" t="s">
+      <c r="B8" s="32"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="62"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="64" t="s">
+      <c r="E8" s="32"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="H8" s="62"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="64" t="s">
+      <c r="H8" s="32"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="K8" s="62"/>
-      <c r="L8" s="62"/>
-      <c r="M8" s="65"/>
-    </row>
-    <row r="9" spans="1:13" ht="29.1" customHeight="1" thickBot="1">
-      <c r="A9" s="51"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="49" t="s">
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="49"/>
+    </row>
+    <row r="9" spans="1:13" ht="31.35" customHeight="1" thickBot="1">
+      <c r="A9" s="34"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="L9" s="49"/>
-      <c r="M9" s="50"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="22"/>
     </row>
     <row r="10" spans="1:13" ht="6.75" customHeight="1">
-      <c r="A10" s="68"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="69"/>
-      <c r="K10" s="70"/>
-      <c r="L10" s="70"/>
-      <c r="M10" s="71"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="30"/>
     </row>
     <row r="11" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A11" s="72" t="s">
+      <c r="A11" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:M4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:M3"/>
     <mergeCell ref="A8:C9"/>
     <mergeCell ref="D8:F9"/>
     <mergeCell ref="G8:I9"/>
@@ -2673,16 +2683,6 @@
     <mergeCell ref="J8:M8"/>
     <mergeCell ref="D6:M6"/>
     <mergeCell ref="K9:L9"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:M4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2702,18 +2702,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2908,11 +2908,11 @@
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
+      <c r="B22" s="71"/>
+      <c r="C22" s="71"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2979,11 +2979,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="27" t="s">
+      <c r="A31" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
+      <c r="B31" s="71"/>
+      <c r="C31" s="71"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3082,11 +3082,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="28" t="s">
+      <c r="A42" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3187,28 +3187,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="22" t="s">
+      <c r="B52" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="23"/>
+      <c r="C52" s="67"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="23" t="s">
+      <c r="B53" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="23"/>
+      <c r="C53" s="67"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="23" t="s">
+      <c r="B54" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="23"/>
+      <c r="C54" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D9A285-1246-4E41-B96B-BDA7850D5C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15D11A7-71F0-4A92-9783-6E5ACD322335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1478,18 +1478,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1859,7 +1853,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1911,153 +1905,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2070,14 +1917,164 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2442,7 +2439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD1811D-72BB-4F54-B90A-4D27DF8394AD}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
@@ -2456,213 +2453,260 @@
     <col min="13" max="13" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:14" ht="32.25" customHeight="1">
+      <c r="A1" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-    </row>
-    <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="65" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="26"/>
+    </row>
+    <row r="2" spans="1:14" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A2" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="63" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63"/>
-      <c r="L2" s="63"/>
-      <c r="M2" s="63"/>
-    </row>
-    <row r="3" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A3" s="61" t="s">
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="26"/>
+    </row>
+    <row r="3" spans="1:14" ht="45.95" customHeight="1">
+      <c r="A3" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="58" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="E3" s="59"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="58" t="s">
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="59"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="58" t="s">
+      <c r="H3" s="31"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="K3" s="59"/>
-      <c r="L3" s="59"/>
-      <c r="M3" s="62"/>
-    </row>
-    <row r="4" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A4" s="39" t="s">
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="26"/>
+    </row>
+    <row r="4" spans="1:14" ht="45.95" customHeight="1">
+      <c r="A4" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="55" t="s">
+      <c r="B4" s="36"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="57"/>
-    </row>
-    <row r="5" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A5" s="39" t="s">
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="26"/>
+    </row>
+    <row r="5" spans="1:14" ht="45.95" customHeight="1">
+      <c r="A5" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="42" t="s">
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="43"/>
-      <c r="F5" s="44" t="s">
+      <c r="E5" s="42"/>
+      <c r="F5" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="45"/>
-    </row>
-    <row r="6" spans="1:13" ht="45.95" customHeight="1">
-      <c r="A6" s="46" t="s">
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="26"/>
+    </row>
+    <row r="6" spans="1:14" ht="45.95" customHeight="1">
+      <c r="A6" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="50" t="s">
+      <c r="B6" s="46"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="48" t="s">
         <v>121</v>
       </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="52"/>
-    </row>
-    <row r="7" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A7" s="18"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="25"/>
-    </row>
-    <row r="8" spans="1:13" ht="26.1" customHeight="1">
-      <c r="A8" s="31" t="s">
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="50"/>
+      <c r="N6" s="26"/>
+    </row>
+    <row r="7" spans="1:14" ht="13.5" customHeight="1">
+      <c r="A7" s="51"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="26"/>
+    </row>
+    <row r="8" spans="1:14" ht="26.1" customHeight="1">
+      <c r="A8" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="37" t="s">
+      <c r="B8" s="59"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="61" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="37" t="s">
+      <c r="E8" s="59"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="61" t="s">
         <v>112</v>
       </c>
-      <c r="H8" s="32"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="37" t="s">
+      <c r="H8" s="59"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61" t="s">
         <v>113</v>
       </c>
-      <c r="K8" s="32"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="49"/>
-    </row>
-    <row r="9" spans="1:13" ht="31.35" customHeight="1" thickBot="1">
-      <c r="A9" s="34"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="53" t="s">
+      <c r="K8" s="59"/>
+      <c r="L8" s="59"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="26"/>
+    </row>
+    <row r="9" spans="1:14" ht="31.35" customHeight="1" thickBot="1">
+      <c r="A9" s="63"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="L9" s="53"/>
-      <c r="M9" s="22"/>
-    </row>
-    <row r="10" spans="1:13" ht="6.75" customHeight="1">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="30"/>
-    </row>
-    <row r="11" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A11" s="54" t="s">
+      <c r="L9" s="24"/>
+      <c r="M9" s="68"/>
+      <c r="N9" s="26"/>
+    </row>
+    <row r="10" spans="1:14" ht="6.75" customHeight="1">
+      <c r="A10" s="69"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="26"/>
+    </row>
+    <row r="11" spans="1:14" ht="27.75" customHeight="1">
+      <c r="A11" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73"/>
+      <c r="J11" s="73"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="26"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="K9:L9"/>
     <mergeCell ref="I2:M2"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:F2"/>
@@ -2679,10 +2723,6 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:M5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="K9:L9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2702,18 +2742,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2908,11 +2948,11 @@
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="71" t="s">
+      <c r="A22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="71"/>
-      <c r="C22" s="71"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -2979,11 +3019,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="71" t="s">
+      <c r="A31" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="71"/>
-      <c r="C31" s="71"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3082,11 +3122,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="72" t="s">
+      <c r="A42" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3187,28 +3227,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="66" t="s">
+      <c r="B52" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="67"/>
+      <c r="C52" s="18"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="67" t="s">
+      <c r="B53" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="67"/>
+      <c r="C53" s="18"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="67" t="s">
+      <c r="B54" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="67"/>
+      <c r="C54" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/source/kaoqing/template/请假申请单模板.xlsx
+++ b/source/kaoqing/template/请假申请单模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hexo\source\kaoqing\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15D11A7-71F0-4A92-9783-6E5ACD322335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D5923D-63A5-4471-A5CC-0DB3D65D077F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{15D765D8-A35B-4240-82F0-B2B1C704E3AC}"/>
   </bookViews>
@@ -1853,7 +1853,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1905,6 +1905,153 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1925,156 +2072,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2439,7 +2436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD1811D-72BB-4F54-B90A-4D27DF8394AD}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="6.625" customWidth="1"/>
@@ -2453,261 +2450,213 @@
     <col min="13" max="13" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="32.25" customHeight="1">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:13" ht="32.25" customHeight="1">
+      <c r="A1" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="26"/>
-    </row>
-    <row r="2" spans="1:14" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A2" s="27" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+    </row>
+    <row r="2" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A2" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="29" t="s">
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="26"/>
-    </row>
-    <row r="3" spans="1:14" ht="45.95" customHeight="1">
-      <c r="A3" s="30" t="s">
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+    </row>
+    <row r="3" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A3" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="33" t="s">
+      <c r="B3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="33" t="s">
+      <c r="E3" s="52"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="51" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="33" t="s">
+      <c r="H3" s="52"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="51" t="s">
         <v>119</v>
       </c>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="26"/>
-    </row>
-    <row r="4" spans="1:14" ht="45.95" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="55"/>
+    </row>
+    <row r="4" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A4" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="38" t="s">
+      <c r="B4" s="46"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="26"/>
-    </row>
-    <row r="5" spans="1:14" ht="45.95" customHeight="1">
-      <c r="A5" s="35" t="s">
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="50"/>
+    </row>
+    <row r="5" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A5" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="41" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="43" t="s">
+      <c r="E5" s="63"/>
+      <c r="F5" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="26"/>
-    </row>
-    <row r="6" spans="1:14" ht="45.95" customHeight="1">
-      <c r="A6" s="45" t="s">
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="65"/>
+    </row>
+    <row r="6" spans="1:13" ht="45.95" customHeight="1">
+      <c r="A6" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="48" t="s">
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="26"/>
-    </row>
-    <row r="7" spans="1:14" ht="13.5" customHeight="1">
-      <c r="A7" s="51"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="54"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="57"/>
-      <c r="N7" s="26"/>
-    </row>
-    <row r="8" spans="1:14" ht="26.1" customHeight="1">
-      <c r="A8" s="58" t="s">
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="39"/>
+    </row>
+    <row r="7" spans="1:13" ht="13.5" customHeight="1">
+      <c r="A7" s="18"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="23"/>
+    </row>
+    <row r="8" spans="1:13" ht="26.1" customHeight="1">
+      <c r="A8" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="61" t="s">
+      <c r="B8" s="35"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="61" t="s">
+      <c r="E8" s="35"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="H8" s="59"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="61" t="s">
+      <c r="H8" s="35"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="62"/>
-      <c r="N8" s="26"/>
-    </row>
-    <row r="9" spans="1:14" ht="31.35" customHeight="1" thickBot="1">
-      <c r="A9" s="63"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="67"/>
-      <c r="K9" s="24" t="s">
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="36"/>
+    </row>
+    <row r="9" spans="1:13" ht="31.35" customHeight="1" thickBot="1">
+      <c r="A9" s="58"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="L9" s="24"/>
-      <c r="M9" s="68"/>
-      <c r="N9" s="26"/>
-    </row>
-    <row r="10" spans="1:14" ht="6.75" customHeight="1">
-      <c r="A10" s="69"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="70"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="71"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="26"/>
-    </row>
-    <row r="11" spans="1:14" ht="27.75" customHeight="1">
-      <c r="A11" s="73" t="s">
+      <c r="L9" s="40"/>
+      <c r="M9" s="26"/>
+    </row>
+    <row r="10" spans="1:13" ht="6.75" customHeight="1">
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="30"/>
+    </row>
+    <row r="11" spans="1:13" ht="27.75" customHeight="1">
+      <c r="A11" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="73"/>
-      <c r="J11" s="73"/>
-      <c r="K11" s="73"/>
-      <c r="L11" s="73"/>
-      <c r="M11" s="73"/>
-      <c r="N11" s="26"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="I2:M2"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:M11"/>
@@ -2723,6 +2672,11 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:M5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="I2:M2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2742,18 +2696,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="20.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -2948,11 +2902,11 @@
       <c r="C21" s="14"/>
     </row>
     <row r="22" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
+      <c r="B22" s="71"/>
+      <c r="C22" s="71"/>
     </row>
     <row r="23" spans="1:3" ht="17.25" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -3019,11 +2973,11 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
+      <c r="B31" s="71"/>
+      <c r="C31" s="71"/>
     </row>
     <row r="32" spans="1:3" ht="17.25" thickBot="1">
       <c r="A32" s="1" t="s">
@@ -3122,11 +3076,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
-      <c r="A42" s="23" t="s">
+      <c r="A42" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" thickBot="1">
       <c r="A43" s="11" t="s">
@@ -3227,28 +3181,28 @@
       <c r="A52">
         <v>1</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B52" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="C52" s="18"/>
+      <c r="C52" s="67"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
         <v>2</v>
       </c>
-      <c r="B53" s="18" t="s">
+      <c r="B53" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="C53" s="18"/>
+      <c r="C53" s="67"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
         <v>3</v>
       </c>
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="18"/>
+      <c r="C54" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="8">
